--- a/Standard_data_structure_v1.4.xlsx
+++ b/Standard_data_structure_v1.4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogleDrive\nkakada\NPCA\documents\interoperability\emr-api\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\dmit\emr-standards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C58090-31BF-4B26-9BF1-E55A7994CFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6989CE-48E5-42C1-8579-F1BC3EDDA077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43170" yWindow="-16515" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="API Objects" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2001" uniqueCount="843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2001" uniqueCount="844">
   <si>
     <t>Model</t>
   </si>
@@ -2577,6 +2577,9 @@
   </si>
   <si>
     <t>Khmer</t>
+  </si>
+  <si>
+    <t>child_difficulty_with_breastfeeding</t>
   </si>
 </sst>
 </file>
@@ -3072,7 +3075,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3323,24 +3326,20 @@
     <xf numFmtId="0" fontId="19" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3369,6 +3368,11 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4146,33 +4150,33 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB1059"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" style="57" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" style="57" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" style="57" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="57" customWidth="1"/>
-    <col min="5" max="5" width="55.140625" style="57" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" style="57" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.88671875" style="57" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="57" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" style="57" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" style="57" customWidth="1"/>
+    <col min="5" max="5" width="55.109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" style="57" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" style="57" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="57" style="57" customWidth="1"/>
-    <col min="9" max="28" width="9.140625" style="2" customWidth="1"/>
-    <col min="29" max="16384" width="12.5703125" style="57"/>
+    <col min="9" max="28" width="9.109375" style="2" customWidth="1"/>
+    <col min="29" max="16384" width="12.5546875" style="57"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="54.75">
-      <c r="A1" s="107" t="s">
+    <row r="1" spans="1:8" ht="52.2">
+      <c r="A1" s="105" t="s">
         <v>757</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-    </row>
-    <row r="2" spans="1:8" ht="29.25">
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+    </row>
+    <row r="2" spans="1:8" ht="28.2">
       <c r="A2" s="27"/>
       <c r="B2" s="70"/>
       <c r="C2" s="70"/>
@@ -4182,19 +4186,19 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" ht="36.75">
-      <c r="A3" s="111" t="s">
+    <row r="3" spans="1:8" ht="37.799999999999997">
+      <c r="A3" s="109" t="s">
         <v>610</v>
       </c>
-      <c r="B3" s="112"/>
-      <c r="C3" s="112"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="113"/>
+      <c r="B3" s="110"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="111"/>
       <c r="F3" s="8"/>
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" ht="23.25">
+    <row r="4" spans="1:8" ht="22.8">
       <c r="A4" s="48" t="s">
         <v>0</v>
       </c>
@@ -4220,7 +4224,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="23.25">
+    <row r="5" spans="1:8" ht="22.8">
       <c r="A5" s="59" t="s">
         <v>5</v>
       </c>
@@ -4236,7 +4240,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:8" ht="23.25">
+    <row r="6" spans="1:8" ht="22.8">
       <c r="A6" s="39"/>
       <c r="B6" s="18" t="s">
         <v>6</v>
@@ -4256,7 +4260,7 @@
       <c r="G6" s="18"/>
       <c r="H6" s="18"/>
     </row>
-    <row r="7" spans="1:8" ht="23.25">
+    <row r="7" spans="1:8" ht="22.8">
       <c r="A7" s="10"/>
       <c r="B7" s="10" t="s">
         <v>10</v>
@@ -4276,7 +4280,7 @@
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
     </row>
-    <row r="8" spans="1:8" ht="23.25">
+    <row r="8" spans="1:8" ht="22.8">
       <c r="A8" s="10"/>
       <c r="B8" s="10" t="s">
         <v>12</v>
@@ -4296,7 +4300,7 @@
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
     </row>
-    <row r="9" spans="1:8" ht="23.25">
+    <row r="9" spans="1:8" ht="22.8">
       <c r="A9" s="10"/>
       <c r="B9" s="10" t="s">
         <v>14</v>
@@ -4320,7 +4324,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="23.25">
+    <row r="10" spans="1:8" ht="22.8">
       <c r="A10" s="10"/>
       <c r="B10" s="10" t="s">
         <v>17</v>
@@ -4340,7 +4344,7 @@
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
     </row>
-    <row r="11" spans="1:8" ht="23.25">
+    <row r="11" spans="1:8" ht="22.8">
       <c r="A11" s="10"/>
       <c r="B11" s="10" t="s">
         <v>20</v>
@@ -4360,7 +4364,7 @@
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
     </row>
-    <row r="12" spans="1:8" ht="23.25">
+    <row r="12" spans="1:8" ht="22.8">
       <c r="A12" s="10"/>
       <c r="B12" s="10" t="s">
         <v>22</v>
@@ -4380,7 +4384,7 @@
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
     </row>
-    <row r="13" spans="1:8" ht="23.25">
+    <row r="13" spans="1:8" ht="22.8">
       <c r="A13" s="10"/>
       <c r="B13" s="10" t="s">
         <v>24</v>
@@ -4400,7 +4404,7 @@
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
     </row>
-    <row r="14" spans="1:8" ht="23.25">
+    <row r="14" spans="1:8" ht="22.8">
       <c r="A14" s="10"/>
       <c r="B14" s="10" t="s">
         <v>27</v>
@@ -4420,7 +4424,7 @@
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
     </row>
-    <row r="15" spans="1:8" ht="23.25">
+    <row r="15" spans="1:8" ht="22.8">
       <c r="A15" s="10"/>
       <c r="B15" s="10" t="s">
         <v>29</v>
@@ -4442,7 +4446,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="23.25">
+    <row r="16" spans="1:8" ht="22.8">
       <c r="A16" s="10"/>
       <c r="B16" s="10" t="s">
         <v>31</v>
@@ -4462,7 +4466,7 @@
       <c r="G16" s="10"/>
       <c r="H16" s="10"/>
     </row>
-    <row r="17" spans="1:8" ht="23.25">
+    <row r="17" spans="1:8" ht="22.8">
       <c r="A17" s="10"/>
       <c r="B17" s="10" t="s">
         <v>33</v>
@@ -4482,7 +4486,7 @@
       <c r="G17" s="10"/>
       <c r="H17" s="10"/>
     </row>
-    <row r="18" spans="1:8" ht="23.25">
+    <row r="18" spans="1:8" ht="22.8">
       <c r="A18" s="10"/>
       <c r="B18" s="10" t="s">
         <v>36</v>
@@ -4502,7 +4506,7 @@
       <c r="G18" s="10"/>
       <c r="H18" s="10"/>
     </row>
-    <row r="19" spans="1:8" ht="23.25">
+    <row r="19" spans="1:8" ht="22.8">
       <c r="A19" s="10"/>
       <c r="B19" s="10" t="s">
         <v>38</v>
@@ -4522,7 +4526,7 @@
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
     </row>
-    <row r="20" spans="1:8" ht="23.25">
+    <row r="20" spans="1:8" ht="22.8">
       <c r="A20" s="10"/>
       <c r="B20" s="10" t="s">
         <v>40</v>
@@ -4542,7 +4546,7 @@
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
     </row>
-    <row r="21" spans="1:8" ht="23.25">
+    <row r="21" spans="1:8" ht="22.8">
       <c r="A21" s="62" t="s">
         <v>42</v>
       </c>
@@ -4558,7 +4562,7 @@
       <c r="G21" s="56"/>
       <c r="H21" s="56"/>
     </row>
-    <row r="22" spans="1:8" ht="23.25">
+    <row r="22" spans="1:8" ht="22.8">
       <c r="A22" s="18"/>
       <c r="B22" s="18" t="s">
         <v>43</v>
@@ -4580,7 +4584,7 @@
       </c>
       <c r="H22" s="18"/>
     </row>
-    <row r="23" spans="1:8" ht="23.25">
+    <row r="23" spans="1:8" ht="22.8">
       <c r="A23" s="10"/>
       <c r="B23" s="10" t="s">
         <v>45</v>
@@ -4600,7 +4604,7 @@
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
     </row>
-    <row r="24" spans="1:8" ht="23.25">
+    <row r="24" spans="1:8" ht="22.8">
       <c r="A24" s="10"/>
       <c r="B24" s="10" t="s">
         <v>47</v>
@@ -4622,7 +4626,7 @@
       </c>
       <c r="H24" s="10"/>
     </row>
-    <row r="25" spans="1:8" ht="23.25">
+    <row r="25" spans="1:8" ht="22.8">
       <c r="A25" s="10"/>
       <c r="B25" s="10" t="s">
         <v>49</v>
@@ -4642,7 +4646,7 @@
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
     </row>
-    <row r="26" spans="1:8" ht="23.25">
+    <row r="26" spans="1:8" ht="22.8">
       <c r="A26" s="10"/>
       <c r="B26" s="10" t="s">
         <v>51</v>
@@ -4664,7 +4668,7 @@
       </c>
       <c r="H26" s="10"/>
     </row>
-    <row r="27" spans="1:8" ht="23.25">
+    <row r="27" spans="1:8" ht="22.8">
       <c r="A27" s="10"/>
       <c r="B27" s="10" t="s">
         <v>53</v>
@@ -4684,7 +4688,7 @@
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
     </row>
-    <row r="28" spans="1:8" ht="23.25">
+    <row r="28" spans="1:8" ht="22.8">
       <c r="A28" s="10"/>
       <c r="B28" s="10" t="s">
         <v>55</v>
@@ -4706,7 +4710,7 @@
       </c>
       <c r="H28" s="10"/>
     </row>
-    <row r="29" spans="1:8" ht="23.25">
+    <row r="29" spans="1:8" ht="22.8">
       <c r="A29" s="10"/>
       <c r="B29" s="10" t="s">
         <v>57</v>
@@ -4726,7 +4730,7 @@
       <c r="G29" s="10"/>
       <c r="H29" s="10"/>
     </row>
-    <row r="30" spans="1:8" ht="23.25">
+    <row r="30" spans="1:8" ht="22.8">
       <c r="A30" s="10"/>
       <c r="B30" s="10" t="s">
         <v>59</v>
@@ -4746,7 +4750,7 @@
       <c r="G30" s="10"/>
       <c r="H30" s="10"/>
     </row>
-    <row r="31" spans="1:8" ht="23.25">
+    <row r="31" spans="1:8" ht="22.8">
       <c r="A31" s="10"/>
       <c r="B31" s="10" t="s">
         <v>61</v>
@@ -4766,7 +4770,7 @@
       <c r="G31" s="10"/>
       <c r="H31" s="10"/>
     </row>
-    <row r="32" spans="1:8" ht="23.25">
+    <row r="32" spans="1:8" ht="22.8">
       <c r="A32" s="10"/>
       <c r="B32" s="10" t="s">
         <v>63</v>
@@ -4786,7 +4790,7 @@
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
     </row>
-    <row r="33" spans="1:28" ht="23.25">
+    <row r="33" spans="1:28" ht="22.8">
       <c r="A33" s="62" t="s">
         <v>65</v>
       </c>
@@ -4802,7 +4806,7 @@
       <c r="G33" s="56"/>
       <c r="H33" s="56"/>
     </row>
-    <row r="34" spans="1:28" ht="23.25">
+    <row r="34" spans="1:28" ht="22.8">
       <c r="A34" s="71"/>
       <c r="B34" s="10" t="s">
         <v>66</v>
@@ -4822,7 +4826,7 @@
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
     </row>
-    <row r="35" spans="1:28" ht="23.25">
+    <row r="35" spans="1:28" ht="22.8">
       <c r="A35" s="10"/>
       <c r="B35" s="10" t="s">
         <v>68</v>
@@ -4842,7 +4846,7 @@
       <c r="G35" s="10"/>
       <c r="H35" s="10"/>
     </row>
-    <row r="36" spans="1:28" ht="23.25">
+    <row r="36" spans="1:28" ht="22.8">
       <c r="A36" s="10"/>
       <c r="B36" s="10" t="s">
         <v>70</v>
@@ -4862,7 +4866,7 @@
       <c r="G36" s="10"/>
       <c r="H36" s="10"/>
     </row>
-    <row r="37" spans="1:28" ht="23.25">
+    <row r="37" spans="1:28" ht="22.8">
       <c r="A37" s="54"/>
       <c r="B37" s="54"/>
       <c r="C37" s="54"/>
@@ -4872,20 +4876,20 @@
       <c r="G37" s="54"/>
       <c r="H37" s="54"/>
     </row>
-    <row r="38" spans="1:28" ht="36.75">
-      <c r="A38" s="111" t="s">
+    <row r="38" spans="1:28" ht="37.799999999999997">
+      <c r="A38" s="109" t="s">
         <v>611</v>
       </c>
-      <c r="B38" s="112"/>
-      <c r="C38" s="112"/>
-      <c r="D38" s="112"/>
-      <c r="E38" s="113"/>
+      <c r="B38" s="110"/>
+      <c r="C38" s="110"/>
+      <c r="D38" s="110"/>
+      <c r="E38" s="111"/>
       <c r="F38" s="69"/>
       <c r="G38" s="69"/>
       <c r="H38" s="69"/>
       <c r="I38" s="8"/>
     </row>
-    <row r="39" spans="1:28" ht="23.25">
+    <row r="39" spans="1:28" ht="22.8">
       <c r="A39" s="48" t="s">
         <v>0</v>
       </c>
@@ -4909,7 +4913,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="40" spans="1:28" s="77" customFormat="1" ht="23.25">
+    <row r="40" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A40" s="29" t="s">
         <v>589</v>
       </c>
@@ -4945,7 +4949,7 @@
       <c r="AA40" s="4"/>
       <c r="AB40" s="4"/>
     </row>
-    <row r="41" spans="1:28" ht="23.25">
+    <row r="41" spans="1:28" ht="22.8">
       <c r="A41" s="10"/>
       <c r="B41" s="10" t="s">
         <v>72</v>
@@ -4967,7 +4971,7 @@
       </c>
       <c r="H41" s="10"/>
     </row>
-    <row r="42" spans="1:28" ht="23.25">
+    <row r="42" spans="1:28" ht="22.8">
       <c r="A42" s="10"/>
       <c r="B42" s="10" t="s">
         <v>66</v>
@@ -4987,7 +4991,7 @@
       <c r="G42" s="10"/>
       <c r="H42" s="10"/>
     </row>
-    <row r="43" spans="1:28" ht="23.25">
+    <row r="43" spans="1:28" ht="22.8">
       <c r="A43" s="10"/>
       <c r="B43" s="10" t="s">
         <v>6</v>
@@ -5007,7 +5011,7 @@
       <c r="G43" s="10"/>
       <c r="H43" s="10"/>
     </row>
-    <row r="44" spans="1:28" ht="23.25">
+    <row r="44" spans="1:28" ht="22.8">
       <c r="A44" s="10"/>
       <c r="B44" s="10" t="s">
         <v>74</v>
@@ -5029,7 +5033,7 @@
       </c>
       <c r="H44" s="10"/>
     </row>
-    <row r="45" spans="1:28" ht="23.25">
+    <row r="45" spans="1:28" ht="22.8">
       <c r="A45" s="10"/>
       <c r="B45" s="10" t="s">
         <v>76</v>
@@ -5053,7 +5057,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="46" spans="1:28" ht="23.25">
+    <row r="46" spans="1:28" ht="22.8">
       <c r="A46" s="10"/>
       <c r="B46" s="10" t="s">
         <v>78</v>
@@ -5077,7 +5081,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="47" spans="1:28" ht="23.25">
+    <row r="47" spans="1:28" ht="22.8">
       <c r="A47" s="10"/>
       <c r="B47" s="10" t="s">
         <v>80</v>
@@ -5099,7 +5103,7 @@
       </c>
       <c r="H47" s="10"/>
     </row>
-    <row r="48" spans="1:28" ht="23.25">
+    <row r="48" spans="1:28" ht="22.8">
       <c r="A48" s="10"/>
       <c r="B48" s="10" t="s">
         <v>82</v>
@@ -5119,7 +5123,7 @@
       <c r="G48" s="10"/>
       <c r="H48" s="10"/>
     </row>
-    <row r="49" spans="1:9" ht="23.25">
+    <row r="49" spans="1:9" ht="22.8">
       <c r="A49" s="10"/>
       <c r="B49" s="10" t="s">
         <v>84</v>
@@ -5141,7 +5145,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="23.25">
+    <row r="50" spans="1:9" ht="22.8">
       <c r="A50" s="10"/>
       <c r="B50" s="10" t="s">
         <v>86</v>
@@ -5161,7 +5165,7 @@
       <c r="G50" s="10"/>
       <c r="H50" s="10"/>
     </row>
-    <row r="51" spans="1:9" ht="23.25">
+    <row r="51" spans="1:9" ht="22.8">
       <c r="A51" s="10"/>
       <c r="B51" s="10" t="s">
         <v>38</v>
@@ -5181,7 +5185,7 @@
       <c r="G51" s="10"/>
       <c r="H51" s="10"/>
     </row>
-    <row r="52" spans="1:9" ht="23.25">
+    <row r="52" spans="1:9" ht="22.8">
       <c r="A52" s="10"/>
       <c r="B52" s="10" t="s">
         <v>40</v>
@@ -5201,7 +5205,7 @@
       <c r="G52" s="10"/>
       <c r="H52" s="10"/>
     </row>
-    <row r="53" spans="1:9" ht="23.25">
+    <row r="53" spans="1:9" ht="22.8">
       <c r="A53" s="54"/>
       <c r="B53" s="54"/>
       <c r="C53" s="54"/>
@@ -5211,33 +5215,33 @@
       <c r="G53" s="54"/>
       <c r="H53" s="54"/>
     </row>
-    <row r="54" spans="1:9" ht="36.75">
-      <c r="A54" s="104" t="s">
+    <row r="54" spans="1:9" ht="37.799999999999997">
+      <c r="A54" s="102" t="s">
         <v>612</v>
       </c>
-      <c r="B54" s="105"/>
-      <c r="C54" s="105"/>
-      <c r="D54" s="105"/>
-      <c r="E54" s="106"/>
+      <c r="B54" s="103"/>
+      <c r="C54" s="103"/>
+      <c r="D54" s="103"/>
+      <c r="E54" s="104"/>
       <c r="F54" s="23"/>
       <c r="G54" s="23"/>
       <c r="H54" s="23"/>
       <c r="I54" s="8"/>
     </row>
-    <row r="55" spans="1:9" ht="33">
-      <c r="A55" s="108" t="s">
+    <row r="55" spans="1:9" ht="33.6">
+      <c r="A55" s="106" t="s">
         <v>613</v>
       </c>
-      <c r="B55" s="109"/>
-      <c r="C55" s="109"/>
-      <c r="D55" s="109"/>
-      <c r="E55" s="110"/>
+      <c r="B55" s="107"/>
+      <c r="C55" s="107"/>
+      <c r="D55" s="107"/>
+      <c r="E55" s="108"/>
       <c r="F55" s="69"/>
       <c r="G55" s="69"/>
       <c r="H55" s="69"/>
       <c r="I55" s="8"/>
     </row>
-    <row r="56" spans="1:9" ht="23.25">
+    <row r="56" spans="1:9" ht="22.8">
       <c r="A56" s="48" t="s">
         <v>0</v>
       </c>
@@ -5260,7 +5264,7 @@
       </c>
       <c r="I56" s="8"/>
     </row>
-    <row r="57" spans="1:9" ht="23.25">
+    <row r="57" spans="1:9" ht="22.8">
       <c r="A57" s="30" t="s">
         <v>599</v>
       </c>
@@ -5279,7 +5283,7 @@
       </c>
       <c r="I57" s="8"/>
     </row>
-    <row r="58" spans="1:9" ht="23.25">
+    <row r="58" spans="1:9" ht="22.8">
       <c r="A58" s="9"/>
       <c r="B58" s="10" t="s">
         <v>88</v>
@@ -5298,7 +5302,7 @@
       <c r="H58" s="10"/>
       <c r="I58" s="8"/>
     </row>
-    <row r="59" spans="1:9" ht="23.25">
+    <row r="59" spans="1:9" ht="22.8">
       <c r="A59" s="9"/>
       <c r="B59" s="10" t="s">
         <v>348</v>
@@ -5319,7 +5323,7 @@
       <c r="H59" s="10"/>
       <c r="I59" s="8"/>
     </row>
-    <row r="60" spans="1:9" ht="23.25">
+    <row r="60" spans="1:9" ht="22.8">
       <c r="A60" s="10"/>
       <c r="B60" s="10" t="s">
         <v>6</v>
@@ -5340,7 +5344,7 @@
       <c r="H60" s="10"/>
       <c r="I60" s="8"/>
     </row>
-    <row r="61" spans="1:9" ht="23.25">
+    <row r="61" spans="1:9" ht="22.8">
       <c r="A61" s="10"/>
       <c r="B61" s="10" t="s">
         <v>353</v>
@@ -5361,7 +5365,7 @@
       <c r="H61" s="10"/>
       <c r="I61" s="8"/>
     </row>
-    <row r="62" spans="1:9" ht="23.25">
+    <row r="62" spans="1:9" ht="22.8">
       <c r="A62" s="10"/>
       <c r="B62" s="10" t="s">
         <v>12</v>
@@ -5382,7 +5386,7 @@
       <c r="H62" s="10"/>
       <c r="I62" s="8"/>
     </row>
-    <row r="63" spans="1:9" ht="23.25">
+    <row r="63" spans="1:9" ht="22.8">
       <c r="A63" s="10"/>
       <c r="B63" s="10" t="s">
         <v>358</v>
@@ -5403,7 +5407,7 @@
       <c r="H63" s="10"/>
       <c r="I63" s="8"/>
     </row>
-    <row r="64" spans="1:9" ht="23.25">
+    <row r="64" spans="1:9" ht="22.8">
       <c r="A64" s="10"/>
       <c r="B64" s="10" t="s">
         <v>360</v>
@@ -5424,7 +5428,7 @@
       <c r="H64" s="10"/>
       <c r="I64" s="8"/>
     </row>
-    <row r="65" spans="1:28" ht="23.25">
+    <row r="65" spans="1:28" ht="22.8">
       <c r="A65" s="10"/>
       <c r="B65" s="10" t="s">
         <v>363</v>
@@ -5443,7 +5447,7 @@
       <c r="H65" s="10"/>
       <c r="I65" s="8"/>
     </row>
-    <row r="66" spans="1:28" ht="23.25">
+    <row r="66" spans="1:28" ht="22.8">
       <c r="A66" s="10"/>
       <c r="B66" s="10" t="s">
         <v>366</v>
@@ -5464,7 +5468,7 @@
       <c r="H66" s="10"/>
       <c r="I66" s="8"/>
     </row>
-    <row r="67" spans="1:28" ht="23.25">
+    <row r="67" spans="1:28" ht="22.8">
       <c r="A67" s="10"/>
       <c r="B67" s="10" t="s">
         <v>103</v>
@@ -5485,7 +5489,7 @@
       <c r="H67" s="10"/>
       <c r="I67" s="8"/>
     </row>
-    <row r="68" spans="1:28" ht="23.25">
+    <row r="68" spans="1:28" ht="22.8">
       <c r="A68" s="10"/>
       <c r="B68" s="10" t="s">
         <v>38</v>
@@ -5506,7 +5510,7 @@
       <c r="H68" s="10"/>
       <c r="I68" s="8"/>
     </row>
-    <row r="69" spans="1:28" ht="23.25">
+    <row r="69" spans="1:28" ht="22.8">
       <c r="A69" s="10"/>
       <c r="B69" s="10" t="s">
         <v>40</v>
@@ -5527,7 +5531,7 @@
       <c r="H69" s="10"/>
       <c r="I69" s="8"/>
     </row>
-    <row r="70" spans="1:28" s="77" customFormat="1" ht="23.25">
+    <row r="70" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A70" s="31" t="s">
         <v>600</v>
       </c>
@@ -5565,7 +5569,7 @@
       <c r="AA70" s="4"/>
       <c r="AB70" s="4"/>
     </row>
-    <row r="71" spans="1:28" ht="23.25">
+    <row r="71" spans="1:28" ht="22.8">
       <c r="A71" s="9"/>
       <c r="B71" s="10" t="s">
         <v>88</v>
@@ -5586,7 +5590,7 @@
       <c r="H71" s="10"/>
       <c r="I71" s="8"/>
     </row>
-    <row r="72" spans="1:28" ht="23.25">
+    <row r="72" spans="1:28" ht="22.8">
       <c r="A72" s="9"/>
       <c r="B72" s="10" t="s">
         <v>348</v>
@@ -5605,7 +5609,7 @@
       <c r="H72" s="10"/>
       <c r="I72" s="8"/>
     </row>
-    <row r="73" spans="1:28" ht="23.25">
+    <row r="73" spans="1:28" ht="22.8">
       <c r="A73" s="10"/>
       <c r="B73" s="10" t="s">
         <v>6</v>
@@ -5626,7 +5630,7 @@
       <c r="H73" s="10"/>
       <c r="I73" s="8"/>
     </row>
-    <row r="74" spans="1:28" ht="23.25">
+    <row r="74" spans="1:28" ht="22.8">
       <c r="A74" s="10"/>
       <c r="B74" s="10" t="s">
         <v>353</v>
@@ -5645,7 +5649,7 @@
       <c r="H74" s="10"/>
       <c r="I74" s="8"/>
     </row>
-    <row r="75" spans="1:28" ht="23.25">
+    <row r="75" spans="1:28" ht="22.8">
       <c r="A75" s="10"/>
       <c r="B75" s="10" t="s">
         <v>12</v>
@@ -5666,7 +5670,7 @@
       <c r="H75" s="10"/>
       <c r="I75" s="8"/>
     </row>
-    <row r="76" spans="1:28" ht="23.25">
+    <row r="76" spans="1:28" ht="22.8">
       <c r="A76" s="10"/>
       <c r="B76" s="10" t="s">
         <v>358</v>
@@ -5687,7 +5691,7 @@
       <c r="H76" s="10"/>
       <c r="I76" s="8"/>
     </row>
-    <row r="77" spans="1:28" ht="23.25">
+    <row r="77" spans="1:28" ht="22.8">
       <c r="A77" s="10"/>
       <c r="B77" s="10" t="s">
         <v>360</v>
@@ -5708,7 +5712,7 @@
       <c r="H77" s="10"/>
       <c r="I77" s="8"/>
     </row>
-    <row r="78" spans="1:28" ht="23.25">
+    <row r="78" spans="1:28" ht="22.8">
       <c r="A78" s="10"/>
       <c r="B78" s="10" t="s">
         <v>363</v>
@@ -5727,7 +5731,7 @@
       <c r="H78" s="10"/>
       <c r="I78" s="8"/>
     </row>
-    <row r="79" spans="1:28" ht="23.25">
+    <row r="79" spans="1:28" ht="22.8">
       <c r="A79" s="10"/>
       <c r="B79" s="10" t="s">
         <v>366</v>
@@ -5748,7 +5752,7 @@
       <c r="H79" s="10"/>
       <c r="I79" s="8"/>
     </row>
-    <row r="80" spans="1:28" ht="23.25">
+    <row r="80" spans="1:28" ht="22.8">
       <c r="A80" s="10"/>
       <c r="B80" s="10" t="s">
         <v>103</v>
@@ -5769,7 +5773,7 @@
       <c r="H80" s="10"/>
       <c r="I80" s="8"/>
     </row>
-    <row r="81" spans="1:28" ht="23.25">
+    <row r="81" spans="1:28" ht="22.8">
       <c r="A81" s="10"/>
       <c r="B81" s="10" t="s">
         <v>38</v>
@@ -5790,7 +5794,7 @@
       <c r="H81" s="10"/>
       <c r="I81" s="8"/>
     </row>
-    <row r="82" spans="1:28" ht="23.25">
+    <row r="82" spans="1:28" ht="22.8">
       <c r="A82" s="10"/>
       <c r="B82" s="10" t="s">
         <v>40</v>
@@ -5811,7 +5815,7 @@
       <c r="H82" s="10"/>
       <c r="I82" s="8"/>
     </row>
-    <row r="83" spans="1:28" s="77" customFormat="1" ht="23.25">
+    <row r="83" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A83" s="31" t="s">
         <v>373</v>
       </c>
@@ -5849,7 +5853,7 @@
       <c r="AA83" s="4"/>
       <c r="AB83" s="4"/>
     </row>
-    <row r="84" spans="1:28" ht="23.25">
+    <row r="84" spans="1:28" ht="22.8">
       <c r="A84" s="9"/>
       <c r="B84" s="10" t="s">
         <v>88</v>
@@ -5870,7 +5874,7 @@
       <c r="H84" s="10"/>
       <c r="I84" s="8"/>
     </row>
-    <row r="85" spans="1:28" ht="23.25">
+    <row r="85" spans="1:28" ht="22.8">
       <c r="A85" s="9"/>
       <c r="B85" s="10" t="s">
         <v>348</v>
@@ -5889,7 +5893,7 @@
       <c r="H85" s="10"/>
       <c r="I85" s="8"/>
     </row>
-    <row r="86" spans="1:28" ht="23.25">
+    <row r="86" spans="1:28" ht="22.8">
       <c r="A86" s="10"/>
       <c r="B86" s="10" t="s">
         <v>6</v>
@@ -5910,7 +5914,7 @@
       <c r="H86" s="10"/>
       <c r="I86" s="8"/>
     </row>
-    <row r="87" spans="1:28" ht="23.25">
+    <row r="87" spans="1:28" ht="22.8">
       <c r="A87" s="10"/>
       <c r="B87" s="10" t="s">
         <v>353</v>
@@ -5929,7 +5933,7 @@
       <c r="H87" s="10"/>
       <c r="I87" s="8"/>
     </row>
-    <row r="88" spans="1:28" ht="23.25">
+    <row r="88" spans="1:28" ht="22.8">
       <c r="A88" s="10"/>
       <c r="B88" s="10" t="s">
         <v>12</v>
@@ -5950,7 +5954,7 @@
       <c r="H88" s="10"/>
       <c r="I88" s="8"/>
     </row>
-    <row r="89" spans="1:28" ht="23.25">
+    <row r="89" spans="1:28" ht="22.8">
       <c r="A89" s="10"/>
       <c r="B89" s="10" t="s">
         <v>358</v>
@@ -5971,7 +5975,7 @@
       <c r="H89" s="10"/>
       <c r="I89" s="8"/>
     </row>
-    <row r="90" spans="1:28" ht="23.25">
+    <row r="90" spans="1:28" ht="22.8">
       <c r="A90" s="10"/>
       <c r="B90" s="10" t="s">
         <v>360</v>
@@ -5992,7 +5996,7 @@
       <c r="H90" s="10"/>
       <c r="I90" s="8"/>
     </row>
-    <row r="91" spans="1:28" ht="23.25">
+    <row r="91" spans="1:28" ht="22.8">
       <c r="A91" s="10"/>
       <c r="B91" s="10" t="s">
         <v>363</v>
@@ -6011,7 +6015,7 @@
       <c r="H91" s="10"/>
       <c r="I91" s="8"/>
     </row>
-    <row r="92" spans="1:28" ht="23.25">
+    <row r="92" spans="1:28" ht="22.8">
       <c r="A92" s="17"/>
       <c r="B92" s="17" t="s">
         <v>375</v>
@@ -6032,7 +6036,7 @@
       <c r="H92" s="10"/>
       <c r="I92" s="8"/>
     </row>
-    <row r="93" spans="1:28" ht="23.25">
+    <row r="93" spans="1:28" ht="22.8">
       <c r="A93" s="10"/>
       <c r="B93" s="10" t="s">
         <v>366</v>
@@ -6053,7 +6057,7 @@
       <c r="H93" s="10"/>
       <c r="I93" s="8"/>
     </row>
-    <row r="94" spans="1:28" ht="23.25">
+    <row r="94" spans="1:28" ht="22.8">
       <c r="A94" s="10"/>
       <c r="B94" s="10" t="s">
         <v>103</v>
@@ -6074,7 +6078,7 @@
       <c r="H94" s="10"/>
       <c r="I94" s="8"/>
     </row>
-    <row r="95" spans="1:28" ht="23.25">
+    <row r="95" spans="1:28" ht="22.8">
       <c r="A95" s="10"/>
       <c r="B95" s="10" t="s">
         <v>38</v>
@@ -6095,7 +6099,7 @@
       <c r="H95" s="10"/>
       <c r="I95" s="8"/>
     </row>
-    <row r="96" spans="1:28" ht="23.25">
+    <row r="96" spans="1:28" ht="22.8">
       <c r="A96" s="10"/>
       <c r="B96" s="10" t="s">
         <v>40</v>
@@ -6116,7 +6120,7 @@
       <c r="H96" s="10"/>
       <c r="I96" s="8"/>
     </row>
-    <row r="97" spans="1:9" ht="23.25">
+    <row r="97" spans="1:9" ht="22.8">
       <c r="A97" s="54"/>
       <c r="B97" s="54"/>
       <c r="C97" s="54"/>
@@ -6127,20 +6131,20 @@
       <c r="H97" s="54"/>
       <c r="I97" s="8"/>
     </row>
-    <row r="98" spans="1:9" ht="33">
-      <c r="A98" s="108" t="s">
+    <row r="98" spans="1:9" ht="33.6">
+      <c r="A98" s="106" t="s">
         <v>614</v>
       </c>
-      <c r="B98" s="109"/>
-      <c r="C98" s="109"/>
-      <c r="D98" s="109"/>
-      <c r="E98" s="110"/>
+      <c r="B98" s="107"/>
+      <c r="C98" s="107"/>
+      <c r="D98" s="107"/>
+      <c r="E98" s="108"/>
       <c r="F98" s="69"/>
       <c r="G98" s="69"/>
       <c r="H98" s="69"/>
       <c r="I98" s="8"/>
     </row>
-    <row r="99" spans="1:9" ht="23.25">
+    <row r="99" spans="1:9" ht="22.8">
       <c r="A99" s="48" t="s">
         <v>0</v>
       </c>
@@ -6163,7 +6167,7 @@
       </c>
       <c r="I99" s="8"/>
     </row>
-    <row r="100" spans="1:9" ht="23.25">
+    <row r="100" spans="1:9" ht="22.8">
       <c r="A100" s="32" t="s">
         <v>609</v>
       </c>
@@ -6182,7 +6186,7 @@
       </c>
       <c r="I100" s="8"/>
     </row>
-    <row r="101" spans="1:9" ht="23.25">
+    <row r="101" spans="1:9" ht="22.8">
       <c r="A101" s="9"/>
       <c r="B101" s="10" t="s">
         <v>88</v>
@@ -6203,7 +6207,7 @@
       <c r="H101" s="10"/>
       <c r="I101" s="8"/>
     </row>
-    <row r="102" spans="1:9" ht="23.25">
+    <row r="102" spans="1:9" ht="22.8">
       <c r="A102" s="10"/>
       <c r="B102" s="10" t="s">
         <v>90</v>
@@ -6226,7 +6230,7 @@
       </c>
       <c r="I102" s="8"/>
     </row>
-    <row r="103" spans="1:9" ht="23.25">
+    <row r="103" spans="1:9" ht="22.8">
       <c r="A103" s="10"/>
       <c r="B103" s="10" t="s">
         <v>348</v>
@@ -6247,7 +6251,7 @@
       <c r="H103" s="11"/>
       <c r="I103" s="8"/>
     </row>
-    <row r="104" spans="1:9" ht="23.25">
+    <row r="104" spans="1:9" ht="22.8">
       <c r="A104" s="10"/>
       <c r="B104" s="10" t="s">
         <v>6</v>
@@ -6268,7 +6272,7 @@
       <c r="H104" s="10"/>
       <c r="I104" s="8"/>
     </row>
-    <row r="105" spans="1:9" ht="23.25">
+    <row r="105" spans="1:9" ht="22.8">
       <c r="A105" s="10"/>
       <c r="B105" s="10" t="s">
         <v>353</v>
@@ -6289,7 +6293,7 @@
       <c r="H105" s="10"/>
       <c r="I105" s="8"/>
     </row>
-    <row r="106" spans="1:9" ht="23.25">
+    <row r="106" spans="1:9" ht="22.8">
       <c r="A106" s="10"/>
       <c r="B106" s="10" t="s">
         <v>379</v>
@@ -6310,7 +6314,7 @@
       <c r="H106" s="10"/>
       <c r="I106" s="8"/>
     </row>
-    <row r="107" spans="1:9" ht="23.25">
+    <row r="107" spans="1:9" ht="22.8">
       <c r="A107" s="10"/>
       <c r="B107" s="10" t="s">
         <v>358</v>
@@ -6331,7 +6335,7 @@
       <c r="H107" s="10"/>
       <c r="I107" s="8"/>
     </row>
-    <row r="108" spans="1:9" ht="23.25">
+    <row r="108" spans="1:9" ht="22.8">
       <c r="A108" s="10"/>
       <c r="B108" s="10" t="s">
         <v>360</v>
@@ -6352,7 +6356,7 @@
       <c r="H108" s="10"/>
       <c r="I108" s="8"/>
     </row>
-    <row r="109" spans="1:9" ht="23.25">
+    <row r="109" spans="1:9" ht="22.8">
       <c r="A109" s="10"/>
       <c r="B109" s="10" t="s">
         <v>363</v>
@@ -6373,7 +6377,7 @@
       <c r="H109" s="10"/>
       <c r="I109" s="8"/>
     </row>
-    <row r="110" spans="1:9" ht="23.25">
+    <row r="110" spans="1:9" ht="22.8">
       <c r="A110" s="10"/>
       <c r="B110" s="10" t="s">
         <v>255</v>
@@ -6394,7 +6398,7 @@
       <c r="H110" s="10"/>
       <c r="I110" s="8"/>
     </row>
-    <row r="111" spans="1:9" ht="23.25">
+    <row r="111" spans="1:9" ht="22.8">
       <c r="A111" s="17"/>
       <c r="B111" s="10" t="s">
         <v>386</v>
@@ -6415,7 +6419,7 @@
       <c r="H111" s="10"/>
       <c r="I111" s="8"/>
     </row>
-    <row r="112" spans="1:9" ht="23.25">
+    <row r="112" spans="1:9" ht="22.8">
       <c r="A112" s="17"/>
       <c r="B112" s="10" t="s">
         <v>389</v>
@@ -6436,7 +6440,7 @@
       <c r="H112" s="10"/>
       <c r="I112" s="8"/>
     </row>
-    <row r="113" spans="1:9" ht="23.25">
+    <row r="113" spans="1:9" ht="22.8">
       <c r="A113" s="17"/>
       <c r="B113" s="10" t="s">
         <v>391</v>
@@ -6457,7 +6461,7 @@
       <c r="H113" s="10"/>
       <c r="I113" s="8"/>
     </row>
-    <row r="114" spans="1:9" ht="23.25">
+    <row r="114" spans="1:9" ht="22.8">
       <c r="A114" s="17"/>
       <c r="B114" s="10" t="s">
         <v>393</v>
@@ -6478,7 +6482,7 @@
       <c r="H114" s="10"/>
       <c r="I114" s="8"/>
     </row>
-    <row r="115" spans="1:9" ht="23.25">
+    <row r="115" spans="1:9" ht="22.8">
       <c r="A115" s="17"/>
       <c r="B115" s="10" t="s">
         <v>396</v>
@@ -6499,7 +6503,7 @@
       <c r="H115" s="10"/>
       <c r="I115" s="8"/>
     </row>
-    <row r="116" spans="1:9" ht="23.25">
+    <row r="116" spans="1:9" ht="22.8">
       <c r="A116" s="17"/>
       <c r="B116" s="10" t="s">
         <v>398</v>
@@ -6520,7 +6524,7 @@
       <c r="H116" s="10"/>
       <c r="I116" s="8"/>
     </row>
-    <row r="117" spans="1:9" ht="23.25">
+    <row r="117" spans="1:9" ht="22.8">
       <c r="A117" s="17"/>
       <c r="B117" s="10" t="s">
         <v>400</v>
@@ -6541,7 +6545,7 @@
       <c r="H117" s="10"/>
       <c r="I117" s="8"/>
     </row>
-    <row r="118" spans="1:9" ht="23.25">
+    <row r="118" spans="1:9" ht="22.8">
       <c r="A118" s="17"/>
       <c r="B118" s="10" t="s">
         <v>403</v>
@@ -6562,7 +6566,7 @@
       <c r="H118" s="10"/>
       <c r="I118" s="8"/>
     </row>
-    <row r="119" spans="1:9" ht="23.25">
+    <row r="119" spans="1:9" ht="22.8">
       <c r="A119" s="17"/>
       <c r="B119" s="10" t="s">
         <v>406</v>
@@ -6583,7 +6587,7 @@
       <c r="H119" s="10"/>
       <c r="I119" s="8"/>
     </row>
-    <row r="120" spans="1:9" ht="23.25">
+    <row r="120" spans="1:9" ht="22.8">
       <c r="A120" s="17"/>
       <c r="B120" s="10" t="s">
         <v>409</v>
@@ -6604,7 +6608,7 @@
       <c r="H120" s="10"/>
       <c r="I120" s="8"/>
     </row>
-    <row r="121" spans="1:9" ht="23.25">
+    <row r="121" spans="1:9" ht="22.8">
       <c r="A121" s="17"/>
       <c r="B121" s="10" t="s">
         <v>412</v>
@@ -6625,7 +6629,7 @@
       <c r="H121" s="10"/>
       <c r="I121" s="23"/>
     </row>
-    <row r="122" spans="1:9" ht="23.25">
+    <row r="122" spans="1:9" ht="22.8">
       <c r="A122" s="17"/>
       <c r="B122" s="10" t="s">
         <v>414</v>
@@ -6646,7 +6650,7 @@
       <c r="H122" s="10"/>
       <c r="I122" s="23"/>
     </row>
-    <row r="123" spans="1:9" ht="23.25">
+    <row r="123" spans="1:9" ht="22.8">
       <c r="A123" s="17"/>
       <c r="B123" s="10" t="s">
         <v>416</v>
@@ -6667,7 +6671,7 @@
       <c r="H123" s="10"/>
       <c r="I123" s="23"/>
     </row>
-    <row r="124" spans="1:9" ht="23.25">
+    <row r="124" spans="1:9" ht="22.8">
       <c r="A124" s="17"/>
       <c r="B124" s="10" t="s">
         <v>418</v>
@@ -6688,7 +6692,7 @@
       <c r="H124" s="10"/>
       <c r="I124" s="23"/>
     </row>
-    <row r="125" spans="1:9" ht="23.25">
+    <row r="125" spans="1:9" ht="22.8">
       <c r="A125" s="10"/>
       <c r="B125" s="10" t="s">
         <v>38</v>
@@ -6709,7 +6713,7 @@
       <c r="H125" s="10"/>
       <c r="I125" s="23"/>
     </row>
-    <row r="126" spans="1:9" ht="23.25">
+    <row r="126" spans="1:9" ht="22.8">
       <c r="A126" s="10"/>
       <c r="B126" s="10" t="s">
         <v>40</v>
@@ -6730,7 +6734,7 @@
       <c r="H126" s="10"/>
       <c r="I126" s="8"/>
     </row>
-    <row r="127" spans="1:9" ht="23.25">
+    <row r="127" spans="1:9" ht="22.8">
       <c r="A127" s="68" t="s">
         <v>420</v>
       </c>
@@ -6747,7 +6751,7 @@
       <c r="H127" s="10"/>
       <c r="I127" s="8"/>
     </row>
-    <row r="128" spans="1:9" ht="23.25">
+    <row r="128" spans="1:9" ht="22.8">
       <c r="A128" s="17"/>
       <c r="B128" s="10" t="s">
         <v>422</v>
@@ -6768,7 +6772,7 @@
       <c r="H128" s="10"/>
       <c r="I128" s="8"/>
     </row>
-    <row r="129" spans="1:28" s="77" customFormat="1" ht="23.25">
+    <row r="129" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A129" s="31" t="s">
         <v>424</v>
       </c>
@@ -6806,7 +6810,7 @@
       <c r="AA129" s="4"/>
       <c r="AB129" s="4"/>
     </row>
-    <row r="130" spans="1:28" ht="23.25">
+    <row r="130" spans="1:28" ht="22.8">
       <c r="A130" s="9"/>
       <c r="B130" s="10" t="s">
         <v>88</v>
@@ -6826,7 +6830,7 @@
       <c r="G130" s="10"/>
       <c r="H130" s="10"/>
     </row>
-    <row r="131" spans="1:28" ht="23.25">
+    <row r="131" spans="1:28" ht="22.8">
       <c r="A131" s="71"/>
       <c r="B131" s="10" t="s">
         <v>90</v>
@@ -6848,7 +6852,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="132" spans="1:28" ht="23.25">
+    <row r="132" spans="1:28" ht="22.8">
       <c r="A132" s="10"/>
       <c r="B132" s="10" t="s">
         <v>6</v>
@@ -6868,7 +6872,7 @@
       <c r="G132" s="10"/>
       <c r="H132" s="10"/>
     </row>
-    <row r="133" spans="1:28" ht="23.25">
+    <row r="133" spans="1:28" ht="22.8">
       <c r="A133" s="10"/>
       <c r="B133" s="10" t="s">
         <v>360</v>
@@ -6888,7 +6892,7 @@
       <c r="G133" s="10"/>
       <c r="H133" s="10"/>
     </row>
-    <row r="134" spans="1:28" ht="23.25">
+    <row r="134" spans="1:28" ht="22.8">
       <c r="A134" s="10"/>
       <c r="B134" s="10" t="s">
         <v>363</v>
@@ -6908,7 +6912,7 @@
       <c r="G134" s="10"/>
       <c r="H134" s="10"/>
     </row>
-    <row r="135" spans="1:28" ht="23.25">
+    <row r="135" spans="1:28" ht="22.8">
       <c r="A135" s="10"/>
       <c r="B135" s="10" t="s">
         <v>366</v>
@@ -6928,7 +6932,7 @@
       <c r="G135" s="10"/>
       <c r="H135" s="10"/>
     </row>
-    <row r="136" spans="1:28" ht="23.25">
+    <row r="136" spans="1:28" ht="22.8">
       <c r="A136" s="10"/>
       <c r="B136" s="10" t="s">
         <v>103</v>
@@ -6948,7 +6952,7 @@
       <c r="G136" s="10"/>
       <c r="H136" s="10"/>
     </row>
-    <row r="137" spans="1:28" ht="23.25">
+    <row r="137" spans="1:28" ht="22.8">
       <c r="A137" s="10"/>
       <c r="B137" s="10" t="s">
         <v>38</v>
@@ -6968,7 +6972,7 @@
       <c r="G137" s="10"/>
       <c r="H137" s="10"/>
     </row>
-    <row r="138" spans="1:28" ht="23.25">
+    <row r="138" spans="1:28" ht="22.8">
       <c r="A138" s="10"/>
       <c r="B138" s="10" t="s">
         <v>40</v>
@@ -6988,7 +6992,7 @@
       <c r="G138" s="10"/>
       <c r="H138" s="10"/>
     </row>
-    <row r="139" spans="1:28" ht="23.25">
+    <row r="139" spans="1:28" ht="22.8">
       <c r="A139" s="10"/>
       <c r="B139" s="10"/>
       <c r="C139" s="10"/>
@@ -6998,19 +7002,19 @@
       <c r="G139" s="10"/>
       <c r="H139" s="10"/>
     </row>
-    <row r="140" spans="1:28" ht="33">
-      <c r="A140" s="108" t="s">
+    <row r="140" spans="1:28" ht="33.6">
+      <c r="A140" s="106" t="s">
         <v>615</v>
       </c>
-      <c r="B140" s="109"/>
-      <c r="C140" s="109"/>
-      <c r="D140" s="109"/>
-      <c r="E140" s="110"/>
+      <c r="B140" s="107"/>
+      <c r="C140" s="107"/>
+      <c r="D140" s="107"/>
+      <c r="E140" s="108"/>
       <c r="F140" s="10"/>
       <c r="G140" s="10"/>
       <c r="H140" s="10"/>
     </row>
-    <row r="141" spans="1:28" ht="23.25">
+    <row r="141" spans="1:28" ht="22.8">
       <c r="A141" s="48" t="s">
         <v>0</v>
       </c>
@@ -7032,7 +7036,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="142" spans="1:28" s="77" customFormat="1" ht="23.25">
+    <row r="142" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A142" s="30" t="s">
         <v>672</v>
       </c>
@@ -7070,7 +7074,7 @@
       <c r="AA142" s="4"/>
       <c r="AB142" s="4"/>
     </row>
-    <row r="143" spans="1:28" ht="23.25">
+    <row r="143" spans="1:28" ht="22.8">
       <c r="A143" s="9"/>
       <c r="B143" s="10" t="s">
         <v>66</v>
@@ -7090,7 +7094,7 @@
       <c r="G143" s="10"/>
       <c r="H143" s="10"/>
     </row>
-    <row r="144" spans="1:28" ht="23.25">
+    <row r="144" spans="1:28" ht="22.8">
       <c r="A144" s="9"/>
       <c r="B144" s="10" t="s">
         <v>88</v>
@@ -7110,7 +7114,7 @@
       <c r="G144" s="10"/>
       <c r="H144" s="10"/>
     </row>
-    <row r="145" spans="1:28" ht="23.25">
+    <row r="145" spans="1:28" ht="22.8">
       <c r="A145" s="10"/>
       <c r="B145" s="10" t="s">
         <v>6</v>
@@ -7130,7 +7134,7 @@
       <c r="G145" s="10"/>
       <c r="H145" s="10"/>
     </row>
-    <row r="146" spans="1:28" ht="23.25">
+    <row r="146" spans="1:28" ht="22.8">
       <c r="A146" s="10"/>
       <c r="B146" s="10" t="s">
         <v>92</v>
@@ -7150,7 +7154,7 @@
       <c r="G146" s="10"/>
       <c r="H146" s="10"/>
     </row>
-    <row r="147" spans="1:28" ht="23.25">
+    <row r="147" spans="1:28" ht="22.8">
       <c r="A147" s="10"/>
       <c r="B147" s="10" t="s">
         <v>96</v>
@@ -7170,7 +7174,7 @@
       <c r="G147" s="10"/>
       <c r="H147" s="10"/>
     </row>
-    <row r="148" spans="1:28" ht="23.25">
+    <row r="148" spans="1:28" ht="22.8">
       <c r="A148" s="10"/>
       <c r="B148" s="10" t="s">
         <v>98</v>
@@ -7190,7 +7194,7 @@
       <c r="G148" s="10"/>
       <c r="H148" s="10"/>
     </row>
-    <row r="149" spans="1:28" ht="23.25">
+    <row r="149" spans="1:28" ht="22.8">
       <c r="A149" s="10"/>
       <c r="B149" s="10" t="s">
         <v>99</v>
@@ -7210,7 +7214,7 @@
       <c r="G149" s="10"/>
       <c r="H149" s="10"/>
     </row>
-    <row r="150" spans="1:28" ht="23.25">
+    <row r="150" spans="1:28" ht="22.8">
       <c r="A150" s="10"/>
       <c r="B150" s="10" t="s">
         <v>101</v>
@@ -7230,7 +7234,7 @@
       <c r="G150" s="10"/>
       <c r="H150" s="10"/>
     </row>
-    <row r="151" spans="1:28" ht="23.25">
+    <row r="151" spans="1:28" ht="22.8">
       <c r="A151" s="10"/>
       <c r="B151" s="10" t="s">
         <v>103</v>
@@ -7250,7 +7254,7 @@
       <c r="G151" s="10"/>
       <c r="H151" s="10"/>
     </row>
-    <row r="152" spans="1:28" s="77" customFormat="1" ht="23.25">
+    <row r="152" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A152" s="34" t="s">
         <v>590</v>
       </c>
@@ -7286,7 +7290,7 @@
       <c r="AA152" s="4"/>
       <c r="AB152" s="4"/>
     </row>
-    <row r="153" spans="1:28" s="58" customFormat="1" ht="23.25">
+    <row r="153" spans="1:28" s="58" customFormat="1" ht="22.8">
       <c r="A153" s="10"/>
       <c r="B153" s="10" t="s">
         <v>90</v>
@@ -7328,7 +7332,7 @@
       <c r="AA153" s="2"/>
       <c r="AB153" s="2"/>
     </row>
-    <row r="154" spans="1:28" ht="23.25">
+    <row r="154" spans="1:28" ht="22.8">
       <c r="A154" s="10"/>
       <c r="B154" s="10" t="s">
         <v>99</v>
@@ -7348,7 +7352,7 @@
       <c r="G154" s="10"/>
       <c r="H154" s="10"/>
     </row>
-    <row r="155" spans="1:28" ht="23.25">
+    <row r="155" spans="1:28" ht="22.8">
       <c r="A155" s="10"/>
       <c r="B155" s="10" t="s">
         <v>101</v>
@@ -7368,7 +7372,7 @@
       <c r="G155" s="10"/>
       <c r="H155" s="10"/>
     </row>
-    <row r="156" spans="1:28" ht="23.25">
+    <row r="156" spans="1:28" ht="22.8">
       <c r="A156" s="10"/>
       <c r="B156" s="10" t="s">
         <v>103</v>
@@ -7388,7 +7392,7 @@
       <c r="G156" s="10"/>
       <c r="H156" s="10"/>
     </row>
-    <row r="157" spans="1:28" s="77" customFormat="1" ht="23.25">
+    <row r="157" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A157" s="65" t="s">
         <v>107</v>
       </c>
@@ -7424,7 +7428,7 @@
       <c r="AA157" s="4"/>
       <c r="AB157" s="4"/>
     </row>
-    <row r="158" spans="1:28" ht="23.25">
+    <row r="158" spans="1:28" ht="22.8">
       <c r="A158" s="37"/>
       <c r="B158" s="38" t="s">
         <v>12</v>
@@ -7446,7 +7450,7 @@
       </c>
       <c r="H158" s="18"/>
     </row>
-    <row r="159" spans="1:28" ht="23.25">
+    <row r="159" spans="1:28" ht="22.8">
       <c r="A159" s="10"/>
       <c r="B159" s="10" t="s">
         <v>109</v>
@@ -7466,7 +7470,7 @@
       <c r="G159" s="10"/>
       <c r="H159" s="10"/>
     </row>
-    <row r="160" spans="1:28" s="77" customFormat="1" ht="23.25">
+    <row r="160" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A160" s="36" t="s">
         <v>112</v>
       </c>
@@ -7504,7 +7508,7 @@
       <c r="AA160" s="4"/>
       <c r="AB160" s="4"/>
     </row>
-    <row r="161" spans="1:28" ht="23.25">
+    <row r="161" spans="1:28" ht="22.8">
       <c r="A161" s="9"/>
       <c r="B161" s="10" t="s">
         <v>66</v>
@@ -7524,7 +7528,7 @@
       <c r="G161" s="10"/>
       <c r="H161" s="10"/>
     </row>
-    <row r="162" spans="1:28" ht="23.25">
+    <row r="162" spans="1:28" ht="22.8">
       <c r="A162" s="9"/>
       <c r="B162" s="10" t="s">
         <v>88</v>
@@ -7544,7 +7548,7 @@
       <c r="G162" s="10"/>
       <c r="H162" s="10"/>
     </row>
-    <row r="163" spans="1:28" ht="23.25">
+    <row r="163" spans="1:28" ht="22.8">
       <c r="A163" s="9"/>
       <c r="B163" s="10" t="s">
         <v>90</v>
@@ -7566,7 +7570,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="164" spans="1:28" ht="23.25">
+    <row r="164" spans="1:28" ht="22.8">
       <c r="A164" s="10"/>
       <c r="B164" s="40" t="s">
         <v>12</v>
@@ -7588,7 +7592,7 @@
       </c>
       <c r="H164" s="18"/>
     </row>
-    <row r="165" spans="1:28" ht="23.25">
+    <row r="165" spans="1:28" ht="22.8">
       <c r="A165" s="10"/>
       <c r="B165" s="10" t="s">
         <v>109</v>
@@ -7608,7 +7612,7 @@
       <c r="G165" s="10"/>
       <c r="H165" s="10"/>
     </row>
-    <row r="166" spans="1:28" s="77" customFormat="1" ht="23.25">
+    <row r="166" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A166" s="35" t="s">
         <v>117</v>
       </c>
@@ -7646,7 +7650,7 @@
       <c r="AA166" s="4"/>
       <c r="AB166" s="4"/>
     </row>
-    <row r="167" spans="1:28" ht="23.25">
+    <row r="167" spans="1:28" ht="22.8">
       <c r="A167" s="9"/>
       <c r="B167" s="10" t="s">
         <v>66</v>
@@ -7666,7 +7670,7 @@
       <c r="G167" s="10"/>
       <c r="H167" s="10"/>
     </row>
-    <row r="168" spans="1:28" ht="23.25">
+    <row r="168" spans="1:28" ht="22.8">
       <c r="A168" s="9"/>
       <c r="B168" s="10" t="s">
         <v>88</v>
@@ -7686,7 +7690,7 @@
       <c r="G168" s="10"/>
       <c r="H168" s="10"/>
     </row>
-    <row r="169" spans="1:28" ht="23.25">
+    <row r="169" spans="1:28" ht="22.8">
       <c r="A169" s="9"/>
       <c r="B169" s="10" t="s">
         <v>90</v>
@@ -7708,7 +7712,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="170" spans="1:28" ht="23.25">
+    <row r="170" spans="1:28" ht="22.8">
       <c r="A170" s="10"/>
       <c r="B170" s="10" t="s">
         <v>12</v>
@@ -7730,7 +7734,7 @@
       </c>
       <c r="H170" s="10"/>
     </row>
-    <row r="171" spans="1:28" ht="23.25">
+    <row r="171" spans="1:28" ht="22.8">
       <c r="A171" s="10"/>
       <c r="B171" s="10" t="s">
         <v>109</v>
@@ -7752,7 +7756,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="172" spans="1:28" ht="23.25">
+    <row r="172" spans="1:28" ht="22.8">
       <c r="A172" s="10"/>
       <c r="B172" s="10" t="s">
         <v>121</v>
@@ -7774,7 +7778,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="173" spans="1:28" ht="23.25">
+    <row r="173" spans="1:28" ht="22.8">
       <c r="A173" s="10"/>
       <c r="B173" s="10" t="s">
         <v>123</v>
@@ -7796,7 +7800,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="174" spans="1:28" s="77" customFormat="1" ht="23.25">
+    <row r="174" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A174" s="35" t="s">
         <v>124</v>
       </c>
@@ -7834,7 +7838,7 @@
       <c r="AA174" s="4"/>
       <c r="AB174" s="4"/>
     </row>
-    <row r="175" spans="1:28" ht="23.25">
+    <row r="175" spans="1:28" ht="22.8">
       <c r="A175" s="9"/>
       <c r="B175" s="10" t="s">
         <v>66</v>
@@ -7854,7 +7858,7 @@
       <c r="G175" s="10"/>
       <c r="H175" s="10"/>
     </row>
-    <row r="176" spans="1:28" ht="23.25">
+    <row r="176" spans="1:28" ht="22.8">
       <c r="A176" s="9"/>
       <c r="B176" s="10" t="s">
         <v>88</v>
@@ -7874,7 +7878,7 @@
       <c r="G176" s="10"/>
       <c r="H176" s="10"/>
     </row>
-    <row r="177" spans="1:28" ht="23.25">
+    <row r="177" spans="1:28" ht="22.8">
       <c r="A177" s="9"/>
       <c r="B177" s="10" t="s">
         <v>90</v>
@@ -7896,7 +7900,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="178" spans="1:28" ht="23.25">
+    <row r="178" spans="1:28" ht="22.8">
       <c r="A178" s="9"/>
       <c r="B178" s="10" t="s">
         <v>125</v>
@@ -7916,7 +7920,7 @@
       <c r="G178" s="9"/>
       <c r="H178" s="10"/>
     </row>
-    <row r="179" spans="1:28" ht="23.25">
+    <row r="179" spans="1:28" ht="22.8">
       <c r="A179" s="10"/>
       <c r="B179" s="10" t="s">
         <v>127</v>
@@ -7936,7 +7940,7 @@
       <c r="G179" s="10"/>
       <c r="H179" s="10"/>
     </row>
-    <row r="180" spans="1:28" ht="23.25">
+    <row r="180" spans="1:28" ht="22.8">
       <c r="A180" s="9"/>
       <c r="B180" s="10" t="s">
         <v>129</v>
@@ -7956,7 +7960,7 @@
       <c r="G180" s="10"/>
       <c r="H180" s="10"/>
     </row>
-    <row r="181" spans="1:28" ht="23.25">
+    <row r="181" spans="1:28" ht="22.8">
       <c r="A181" s="9"/>
       <c r="B181" s="10" t="s">
         <v>103</v>
@@ -7976,7 +7980,7 @@
       <c r="G181" s="10"/>
       <c r="H181" s="10"/>
     </row>
-    <row r="182" spans="1:28" s="77" customFormat="1" ht="23.25">
+    <row r="182" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A182" s="55" t="s">
         <v>131</v>
       </c>
@@ -8014,7 +8018,7 @@
       <c r="AA182" s="4"/>
       <c r="AB182" s="4"/>
     </row>
-    <row r="183" spans="1:28" ht="23.25">
+    <row r="183" spans="1:28" ht="22.8">
       <c r="A183" s="10"/>
       <c r="B183" s="10" t="s">
         <v>12</v>
@@ -8034,7 +8038,7 @@
       <c r="G183" s="10"/>
       <c r="H183" s="10"/>
     </row>
-    <row r="184" spans="1:28" ht="23.25">
+    <row r="184" spans="1:28" ht="22.8">
       <c r="A184" s="10"/>
       <c r="B184" s="10" t="s">
         <v>134</v>
@@ -8054,7 +8058,7 @@
       <c r="G184" s="10"/>
       <c r="H184" s="10"/>
     </row>
-    <row r="185" spans="1:28" ht="23.25">
+    <row r="185" spans="1:28" ht="22.8">
       <c r="A185" s="10"/>
       <c r="B185" s="10" t="s">
         <v>109</v>
@@ -8074,7 +8078,7 @@
       <c r="G185" s="10"/>
       <c r="H185" s="10"/>
     </row>
-    <row r="186" spans="1:28" ht="23.25">
+    <row r="186" spans="1:28" ht="22.8">
       <c r="A186" s="10"/>
       <c r="B186" s="10" t="s">
         <v>121</v>
@@ -8094,7 +8098,7 @@
       <c r="G186" s="10"/>
       <c r="H186" s="10"/>
     </row>
-    <row r="187" spans="1:28" ht="23.25">
+    <row r="187" spans="1:28" ht="22.8">
       <c r="A187" s="10"/>
       <c r="B187" s="10" t="s">
         <v>123</v>
@@ -8114,7 +8118,7 @@
       <c r="G187" s="10"/>
       <c r="H187" s="10"/>
     </row>
-    <row r="188" spans="1:28" ht="23.25">
+    <row r="188" spans="1:28" ht="22.8">
       <c r="A188" s="10"/>
       <c r="B188" s="10" t="s">
         <v>139</v>
@@ -8134,7 +8138,7 @@
       <c r="G188" s="10"/>
       <c r="H188" s="10"/>
     </row>
-    <row r="189" spans="1:28" ht="23.25">
+    <row r="189" spans="1:28" ht="22.8">
       <c r="A189" s="10"/>
       <c r="B189" s="10" t="s">
         <v>142</v>
@@ -8154,7 +8158,7 @@
       <c r="G189" s="10"/>
       <c r="H189" s="10"/>
     </row>
-    <row r="190" spans="1:28" ht="23.25">
+    <row r="190" spans="1:28" ht="22.8">
       <c r="A190" s="10"/>
       <c r="B190" s="10" t="s">
         <v>145</v>
@@ -8174,7 +8178,7 @@
       <c r="G190" s="10"/>
       <c r="H190" s="10"/>
     </row>
-    <row r="191" spans="1:28" ht="23.25">
+    <row r="191" spans="1:28" ht="22.8">
       <c r="A191" s="10"/>
       <c r="B191" s="10" t="s">
         <v>148</v>
@@ -8194,7 +8198,7 @@
       <c r="G191" s="10"/>
       <c r="H191" s="10"/>
     </row>
-    <row r="192" spans="1:28" ht="23.25">
+    <row r="192" spans="1:28" ht="22.8">
       <c r="A192" s="10"/>
       <c r="B192" s="10" t="s">
         <v>99</v>
@@ -8214,7 +8218,7 @@
       <c r="G192" s="10"/>
       <c r="H192" s="10"/>
     </row>
-    <row r="193" spans="1:28" ht="23.25">
+    <row r="193" spans="1:28" ht="22.8">
       <c r="A193" s="10"/>
       <c r="B193" s="10" t="s">
         <v>101</v>
@@ -8234,7 +8238,7 @@
       <c r="G193" s="10"/>
       <c r="H193" s="10"/>
     </row>
-    <row r="194" spans="1:28" s="77" customFormat="1" ht="23.25">
+    <row r="194" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A194" s="35" t="s">
         <v>156</v>
       </c>
@@ -8272,7 +8276,7 @@
       <c r="AA194" s="4"/>
       <c r="AB194" s="4"/>
     </row>
-    <row r="195" spans="1:28" ht="23.25">
+    <row r="195" spans="1:28" ht="22.8">
       <c r="A195" s="9"/>
       <c r="B195" s="10" t="s">
         <v>66</v>
@@ -8292,7 +8296,7 @@
       <c r="G195" s="10"/>
       <c r="H195" s="10"/>
     </row>
-    <row r="196" spans="1:28" ht="23.25">
+    <row r="196" spans="1:28" ht="22.8">
       <c r="A196" s="9"/>
       <c r="B196" s="10" t="s">
         <v>88</v>
@@ -8312,7 +8316,7 @@
       <c r="G196" s="10"/>
       <c r="H196" s="10"/>
     </row>
-    <row r="197" spans="1:28" ht="23.25">
+    <row r="197" spans="1:28" ht="22.8">
       <c r="A197" s="9"/>
       <c r="B197" s="10" t="s">
         <v>90</v>
@@ -8334,7 +8338,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="198" spans="1:28" ht="23.25">
+    <row r="198" spans="1:28" ht="22.8">
       <c r="A198" s="9"/>
       <c r="B198" s="10" t="s">
         <v>125</v>
@@ -8354,7 +8358,7 @@
       <c r="G198" s="10"/>
       <c r="H198" s="10"/>
     </row>
-    <row r="199" spans="1:28" ht="23.25">
+    <row r="199" spans="1:28" ht="22.8">
       <c r="A199" s="10"/>
       <c r="B199" s="10" t="s">
         <v>127</v>
@@ -8374,7 +8378,7 @@
       <c r="G199" s="10"/>
       <c r="H199" s="10"/>
     </row>
-    <row r="200" spans="1:28" ht="23.25">
+    <row r="200" spans="1:28" ht="22.8">
       <c r="A200" s="9"/>
       <c r="B200" s="10" t="s">
         <v>129</v>
@@ -8394,7 +8398,7 @@
       <c r="G200" s="10"/>
       <c r="H200" s="10"/>
     </row>
-    <row r="201" spans="1:28" ht="23.25">
+    <row r="201" spans="1:28" ht="22.8">
       <c r="A201" s="9"/>
       <c r="B201" s="10" t="s">
         <v>103</v>
@@ -8414,7 +8418,7 @@
       <c r="G201" s="10"/>
       <c r="H201" s="10"/>
     </row>
-    <row r="202" spans="1:28" s="77" customFormat="1" ht="23.25">
+    <row r="202" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A202" s="55" t="s">
         <v>162</v>
       </c>
@@ -8450,7 +8454,7 @@
       <c r="AA202" s="4"/>
       <c r="AB202" s="4"/>
     </row>
-    <row r="203" spans="1:28" ht="23.25">
+    <row r="203" spans="1:28" ht="22.8">
       <c r="A203" s="71"/>
       <c r="B203" s="10" t="s">
         <v>12</v>
@@ -8470,7 +8474,7 @@
       <c r="G203" s="10"/>
       <c r="H203" s="10"/>
     </row>
-    <row r="204" spans="1:28" ht="23.25">
+    <row r="204" spans="1:28" ht="22.8">
       <c r="A204" s="10"/>
       <c r="B204" s="10" t="s">
         <v>134</v>
@@ -8490,7 +8494,7 @@
       <c r="G204" s="10"/>
       <c r="H204" s="10"/>
     </row>
-    <row r="205" spans="1:28" ht="23.25">
+    <row r="205" spans="1:28" ht="22.8">
       <c r="A205" s="10"/>
       <c r="B205" s="10" t="s">
         <v>167</v>
@@ -8510,7 +8514,7 @@
       <c r="G205" s="10"/>
       <c r="H205" s="10"/>
     </row>
-    <row r="206" spans="1:28" ht="23.25">
+    <row r="206" spans="1:28" ht="22.8">
       <c r="A206" s="10"/>
       <c r="B206" s="10" t="s">
         <v>169</v>
@@ -8530,7 +8534,7 @@
       <c r="G206" s="10"/>
       <c r="H206" s="10"/>
     </row>
-    <row r="207" spans="1:28" ht="23.25">
+    <row r="207" spans="1:28" ht="22.8">
       <c r="A207" s="10"/>
       <c r="B207" s="10" t="s">
         <v>172</v>
@@ -8550,7 +8554,7 @@
       <c r="G207" s="10"/>
       <c r="H207" s="10"/>
     </row>
-    <row r="208" spans="1:28" ht="23.25">
+    <row r="208" spans="1:28" ht="22.8">
       <c r="A208" s="10"/>
       <c r="B208" s="10" t="s">
         <v>145</v>
@@ -8570,7 +8574,7 @@
       <c r="G208" s="10"/>
       <c r="H208" s="10"/>
     </row>
-    <row r="209" spans="1:28" ht="23.25">
+    <row r="209" spans="1:28" ht="22.8">
       <c r="A209" s="10"/>
       <c r="B209" s="10" t="s">
         <v>148</v>
@@ -8590,7 +8594,7 @@
       <c r="G209" s="10"/>
       <c r="H209" s="10"/>
     </row>
-    <row r="210" spans="1:28" ht="23.25">
+    <row r="210" spans="1:28" ht="22.8">
       <c r="A210" s="10"/>
       <c r="B210" s="10" t="s">
         <v>99</v>
@@ -8610,7 +8614,7 @@
       <c r="G210" s="10"/>
       <c r="H210" s="10"/>
     </row>
-    <row r="211" spans="1:28" ht="23.25">
+    <row r="211" spans="1:28" ht="22.8">
       <c r="A211" s="10"/>
       <c r="B211" s="10" t="s">
         <v>101</v>
@@ -8630,7 +8634,7 @@
       <c r="G211" s="10"/>
       <c r="H211" s="10"/>
     </row>
-    <row r="212" spans="1:28" s="77" customFormat="1" ht="23.25">
+    <row r="212" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A212" s="50" t="s">
         <v>175</v>
       </c>
@@ -8664,7 +8668,7 @@
       <c r="AA212" s="4"/>
       <c r="AB212" s="4"/>
     </row>
-    <row r="213" spans="1:28" ht="23.25">
+    <row r="213" spans="1:28" ht="22.8">
       <c r="A213" s="9"/>
       <c r="B213" s="10" t="s">
         <v>66</v>
@@ -8684,7 +8688,7 @@
       <c r="G213" s="10"/>
       <c r="H213" s="10"/>
     </row>
-    <row r="214" spans="1:28" ht="23.25">
+    <row r="214" spans="1:28" ht="22.8">
       <c r="A214" s="9"/>
       <c r="B214" s="10" t="s">
         <v>88</v>
@@ -8704,7 +8708,7 @@
       <c r="G214" s="10"/>
       <c r="H214" s="10"/>
     </row>
-    <row r="215" spans="1:28" ht="23.25">
+    <row r="215" spans="1:28" ht="22.8">
       <c r="A215" s="10"/>
       <c r="B215" s="10" t="s">
         <v>90</v>
@@ -8726,7 +8730,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="216" spans="1:28" ht="23.25">
+    <row r="216" spans="1:28" ht="22.8">
       <c r="A216" s="10"/>
       <c r="B216" s="10" t="s">
         <v>176</v>
@@ -8748,7 +8752,7 @@
       </c>
       <c r="H216" s="10"/>
     </row>
-    <row r="217" spans="1:28" ht="23.25">
+    <row r="217" spans="1:28" ht="22.8">
       <c r="A217" s="10"/>
       <c r="B217" s="10" t="s">
         <v>178</v>
@@ -8770,7 +8774,7 @@
       </c>
       <c r="H217" s="10"/>
     </row>
-    <row r="218" spans="1:28" ht="23.25">
+    <row r="218" spans="1:28" ht="22.8">
       <c r="A218" s="10"/>
       <c r="B218" s="10" t="s">
         <v>180</v>
@@ -8790,7 +8794,7 @@
       <c r="G218" s="10"/>
       <c r="H218" s="10"/>
     </row>
-    <row r="219" spans="1:28" ht="23.25">
+    <row r="219" spans="1:28" ht="22.8">
       <c r="A219" s="10"/>
       <c r="B219" s="10" t="s">
         <v>182</v>
@@ -8810,7 +8814,7 @@
       <c r="G219" s="10"/>
       <c r="H219" s="10"/>
     </row>
-    <row r="220" spans="1:28" ht="23.25">
+    <row r="220" spans="1:28" ht="22.8">
       <c r="A220" s="10"/>
       <c r="B220" s="10" t="s">
         <v>184</v>
@@ -8830,7 +8834,7 @@
       <c r="G220" s="10"/>
       <c r="H220" s="10"/>
     </row>
-    <row r="221" spans="1:28" ht="23.25">
+    <row r="221" spans="1:28" ht="22.8">
       <c r="A221" s="10"/>
       <c r="B221" s="10" t="s">
         <v>187</v>
@@ -8850,7 +8854,7 @@
       <c r="G221" s="10"/>
       <c r="H221" s="10"/>
     </row>
-    <row r="222" spans="1:28" ht="23.25">
+    <row r="222" spans="1:28" ht="22.8">
       <c r="A222" s="10"/>
       <c r="B222" s="10" t="s">
         <v>103</v>
@@ -8870,7 +8874,7 @@
       <c r="G222" s="10"/>
       <c r="H222" s="10"/>
     </row>
-    <row r="223" spans="1:28" s="77" customFormat="1" ht="23.25">
+    <row r="223" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A223" s="41" t="s">
         <v>189</v>
       </c>
@@ -8906,7 +8910,7 @@
       <c r="AA223" s="4"/>
       <c r="AB223" s="4"/>
     </row>
-    <row r="224" spans="1:28" ht="23.25">
+    <row r="224" spans="1:28" ht="22.8">
       <c r="A224" s="9"/>
       <c r="B224" s="11" t="s">
         <v>90</v>
@@ -8928,7 +8932,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="225" spans="1:28" ht="23.25">
+    <row r="225" spans="1:28" ht="22.8">
       <c r="A225" s="10"/>
       <c r="B225" s="10" t="s">
         <v>196</v>
@@ -8948,7 +8952,7 @@
       <c r="G225" s="10"/>
       <c r="H225" s="10"/>
     </row>
-    <row r="226" spans="1:28" ht="23.25">
+    <row r="226" spans="1:28" ht="22.8">
       <c r="A226" s="9"/>
       <c r="B226" s="10" t="s">
         <v>190</v>
@@ -8968,7 +8972,7 @@
       <c r="G226" s="10"/>
       <c r="H226" s="10"/>
     </row>
-    <row r="227" spans="1:28" ht="23.25">
+    <row r="227" spans="1:28" ht="22.8">
       <c r="A227" s="10"/>
       <c r="B227" s="10" t="s">
         <v>192</v>
@@ -8988,7 +8992,7 @@
       <c r="G227" s="10"/>
       <c r="H227" s="10"/>
     </row>
-    <row r="228" spans="1:28" ht="23.25">
+    <row r="228" spans="1:28" ht="22.8">
       <c r="A228" s="10"/>
       <c r="B228" s="10" t="s">
         <v>193</v>
@@ -9008,7 +9012,7 @@
       <c r="G228" s="10"/>
       <c r="H228" s="10"/>
     </row>
-    <row r="229" spans="1:28" ht="23.25">
+    <row r="229" spans="1:28" ht="22.8">
       <c r="A229" s="10"/>
       <c r="B229" s="10" t="s">
         <v>195</v>
@@ -9028,7 +9032,7 @@
       <c r="G229" s="10"/>
       <c r="H229" s="10"/>
     </row>
-    <row r="230" spans="1:28" ht="23.25">
+    <row r="230" spans="1:28" ht="22.8">
       <c r="A230" s="10"/>
       <c r="B230" s="10" t="s">
         <v>194</v>
@@ -9048,7 +9052,7 @@
       <c r="G230" s="10"/>
       <c r="H230" s="10"/>
     </row>
-    <row r="231" spans="1:28" ht="23.25">
+    <row r="231" spans="1:28" ht="22.8">
       <c r="A231" s="10"/>
       <c r="B231" s="10" t="s">
         <v>197</v>
@@ -9068,7 +9072,7 @@
       <c r="G231" s="10"/>
       <c r="H231" s="10"/>
     </row>
-    <row r="232" spans="1:28" ht="23.25">
+    <row r="232" spans="1:28" ht="22.8">
       <c r="A232" s="10"/>
       <c r="B232" s="10" t="s">
         <v>198</v>
@@ -9088,7 +9092,7 @@
       <c r="G232" s="10"/>
       <c r="H232" s="10"/>
     </row>
-    <row r="233" spans="1:28" ht="23.25">
+    <row r="233" spans="1:28" ht="22.8">
       <c r="A233" s="10"/>
       <c r="B233" s="10" t="s">
         <v>199</v>
@@ -9108,7 +9112,7 @@
       <c r="G233" s="10"/>
       <c r="H233" s="10"/>
     </row>
-    <row r="234" spans="1:28" s="77" customFormat="1" ht="23.25">
+    <row r="234" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A234" s="51" t="s">
         <v>428</v>
       </c>
@@ -9146,7 +9150,7 @@
       <c r="AA234" s="4"/>
       <c r="AB234" s="4"/>
     </row>
-    <row r="235" spans="1:28" ht="23.25">
+    <row r="235" spans="1:28" ht="22.8">
       <c r="A235" s="10"/>
       <c r="B235" s="10" t="s">
         <v>88</v>
@@ -9166,7 +9170,7 @@
       <c r="G235" s="10"/>
       <c r="H235" s="10"/>
     </row>
-    <row r="236" spans="1:28" ht="23.25">
+    <row r="236" spans="1:28" ht="22.8">
       <c r="A236" s="10"/>
       <c r="B236" s="10" t="s">
         <v>90</v>
@@ -9188,7 +9192,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="237" spans="1:28" ht="23.25">
+    <row r="237" spans="1:28" ht="22.8">
       <c r="A237" s="52"/>
       <c r="B237" s="10" t="s">
         <v>430</v>
@@ -9210,7 +9214,7 @@
       </c>
       <c r="H237" s="3"/>
     </row>
-    <row r="238" spans="1:28" ht="23.25">
+    <row r="238" spans="1:28" ht="22.8">
       <c r="A238" s="52"/>
       <c r="B238" s="10" t="s">
         <v>432</v>
@@ -9232,7 +9236,7 @@
       </c>
       <c r="H238" s="3"/>
     </row>
-    <row r="239" spans="1:28" ht="23.25">
+    <row r="239" spans="1:28" ht="22.8">
       <c r="A239" s="52"/>
       <c r="B239" s="10" t="s">
         <v>434</v>
@@ -9254,7 +9258,7 @@
       </c>
       <c r="H239" s="3"/>
     </row>
-    <row r="240" spans="1:28" s="77" customFormat="1" ht="23.25">
+    <row r="240" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A240" s="42" t="s">
         <v>200</v>
       </c>
@@ -9290,7 +9294,7 @@
       <c r="AA240" s="4"/>
       <c r="AB240" s="4"/>
     </row>
-    <row r="241" spans="1:28" ht="23.25">
+    <row r="241" spans="1:28" ht="22.8">
       <c r="A241" s="9"/>
       <c r="B241" s="10" t="s">
         <v>66</v>
@@ -9310,7 +9314,7 @@
       <c r="G241" s="10"/>
       <c r="H241" s="10"/>
     </row>
-    <row r="242" spans="1:28" ht="23.25">
+    <row r="242" spans="1:28" ht="22.8">
       <c r="A242" s="9"/>
       <c r="B242" s="10" t="s">
         <v>88</v>
@@ -9330,7 +9334,7 @@
       <c r="G242" s="10"/>
       <c r="H242" s="10"/>
     </row>
-    <row r="243" spans="1:28" ht="23.25">
+    <row r="243" spans="1:28" ht="22.8">
       <c r="A243" s="9"/>
       <c r="B243" s="10" t="s">
         <v>90</v>
@@ -9352,7 +9356,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="244" spans="1:28" ht="23.25">
+    <row r="244" spans="1:28" ht="22.8">
       <c r="A244" s="10"/>
       <c r="B244" s="10" t="s">
         <v>6</v>
@@ -9372,7 +9376,7 @@
       <c r="G244" s="10"/>
       <c r="H244" s="10"/>
     </row>
-    <row r="245" spans="1:28" ht="23.25">
+    <row r="245" spans="1:28" ht="22.8">
       <c r="A245" s="10"/>
       <c r="B245" s="10" t="s">
         <v>203</v>
@@ -9392,7 +9396,7 @@
       <c r="G245" s="10"/>
       <c r="H245" s="10"/>
     </row>
-    <row r="246" spans="1:28" ht="23.25">
+    <row r="246" spans="1:28" ht="22.8">
       <c r="A246" s="10"/>
       <c r="B246" s="10" t="s">
         <v>205</v>
@@ -9412,7 +9416,7 @@
       <c r="G246" s="10"/>
       <c r="H246" s="10"/>
     </row>
-    <row r="247" spans="1:28" ht="23.25">
+    <row r="247" spans="1:28" ht="22.8">
       <c r="A247" s="10"/>
       <c r="B247" s="10" t="s">
         <v>103</v>
@@ -9432,7 +9436,7 @@
       <c r="G247" s="10"/>
       <c r="H247" s="10"/>
     </row>
-    <row r="248" spans="1:28" s="77" customFormat="1" ht="23.25">
+    <row r="248" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A248" s="55" t="s">
         <v>207</v>
       </c>
@@ -9468,7 +9472,7 @@
       <c r="AA248" s="4"/>
       <c r="AB248" s="4"/>
     </row>
-    <row r="249" spans="1:28" ht="23.25">
+    <row r="249" spans="1:28" ht="22.8">
       <c r="A249" s="9"/>
       <c r="B249" s="10" t="s">
         <v>6</v>
@@ -9490,7 +9494,7 @@
       </c>
       <c r="H249" s="10"/>
     </row>
-    <row r="250" spans="1:28" ht="23.25">
+    <row r="250" spans="1:28" ht="22.8">
       <c r="A250" s="10"/>
       <c r="B250" s="10" t="s">
         <v>210</v>
@@ -9512,7 +9516,7 @@
       </c>
       <c r="H250" s="10"/>
     </row>
-    <row r="251" spans="1:28" ht="23.25">
+    <row r="251" spans="1:28" ht="22.8">
       <c r="A251" s="10"/>
       <c r="B251" s="10" t="s">
         <v>213</v>
@@ -9532,7 +9536,7 @@
       <c r="G251" s="10"/>
       <c r="H251" s="10"/>
     </row>
-    <row r="252" spans="1:28" ht="23.25">
+    <row r="252" spans="1:28" ht="22.8">
       <c r="A252" s="10"/>
       <c r="B252" s="10" t="s">
         <v>217</v>
@@ -9552,7 +9556,7 @@
       <c r="G252" s="10"/>
       <c r="H252" s="10"/>
     </row>
-    <row r="253" spans="1:28" ht="23.25">
+    <row r="253" spans="1:28" ht="22.8">
       <c r="A253" s="10"/>
       <c r="B253" s="10" t="s">
         <v>220</v>
@@ -9572,7 +9576,7 @@
       <c r="G253" s="10"/>
       <c r="H253" s="10"/>
     </row>
-    <row r="254" spans="1:28" ht="23.25">
+    <row r="254" spans="1:28" ht="22.8">
       <c r="A254" s="10"/>
       <c r="B254" s="10" t="s">
         <v>222</v>
@@ -9592,7 +9596,7 @@
       <c r="G254" s="10"/>
       <c r="H254" s="10"/>
     </row>
-    <row r="255" spans="1:28" ht="23.25">
+    <row r="255" spans="1:28" ht="22.8">
       <c r="A255" s="10"/>
       <c r="B255" s="10" t="s">
         <v>225</v>
@@ -9612,7 +9616,7 @@
       <c r="G255" s="10"/>
       <c r="H255" s="10"/>
     </row>
-    <row r="256" spans="1:28" ht="23.25">
+    <row r="256" spans="1:28" ht="22.8">
       <c r="A256" s="10"/>
       <c r="B256" s="10" t="s">
         <v>227</v>
@@ -9632,7 +9636,7 @@
       <c r="G256" s="10"/>
       <c r="H256" s="10"/>
     </row>
-    <row r="257" spans="1:28" ht="23.25">
+    <row r="257" spans="1:28" ht="22.8">
       <c r="A257" s="10"/>
       <c r="B257" s="10" t="s">
         <v>229</v>
@@ -9652,7 +9656,7 @@
       <c r="G257" s="10"/>
       <c r="H257" s="10"/>
     </row>
-    <row r="258" spans="1:28" ht="23.25">
+    <row r="258" spans="1:28" ht="22.8">
       <c r="A258" s="10"/>
       <c r="B258" s="10" t="s">
         <v>231</v>
@@ -9672,7 +9676,7 @@
       <c r="G258" s="10"/>
       <c r="H258" s="10"/>
     </row>
-    <row r="259" spans="1:28" ht="23.25">
+    <row r="259" spans="1:28" ht="22.8">
       <c r="A259" s="10"/>
       <c r="B259" s="10" t="s">
         <v>235</v>
@@ -9692,7 +9696,7 @@
       <c r="G259" s="10"/>
       <c r="H259" s="10"/>
     </row>
-    <row r="260" spans="1:28" ht="23.25">
+    <row r="260" spans="1:28" ht="22.8">
       <c r="A260" s="10"/>
       <c r="B260" s="10" t="s">
         <v>239</v>
@@ -9710,7 +9714,7 @@
       <c r="G260" s="10"/>
       <c r="H260" s="10"/>
     </row>
-    <row r="261" spans="1:28" s="77" customFormat="1" ht="23.25">
+    <row r="261" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A261" s="55" t="s">
         <v>241</v>
       </c>
@@ -9746,7 +9750,7 @@
       <c r="AA261" s="4"/>
       <c r="AB261" s="4"/>
     </row>
-    <row r="262" spans="1:28" ht="23.25">
+    <row r="262" spans="1:28" ht="22.8">
       <c r="A262" s="10"/>
       <c r="B262" s="10" t="s">
         <v>220</v>
@@ -9764,7 +9768,7 @@
       <c r="G262" s="10"/>
       <c r="H262" s="10"/>
     </row>
-    <row r="263" spans="1:28" ht="23.25">
+    <row r="263" spans="1:28" ht="22.8">
       <c r="A263" s="10"/>
       <c r="B263" s="10" t="s">
         <v>244</v>
@@ -9782,7 +9786,7 @@
       <c r="G263" s="10"/>
       <c r="H263" s="10"/>
     </row>
-    <row r="264" spans="1:28" s="73" customFormat="1" ht="23.25">
+    <row r="264" spans="1:28" s="73" customFormat="1" ht="22.8">
       <c r="A264" s="45" t="s">
         <v>285</v>
       </c>
@@ -9820,7 +9824,7 @@
       <c r="AA264" s="13"/>
       <c r="AB264" s="13"/>
     </row>
-    <row r="265" spans="1:28" ht="23.25">
+    <row r="265" spans="1:28" ht="22.8">
       <c r="A265" s="43" t="s">
         <v>247</v>
       </c>
@@ -9836,7 +9840,7 @@
       <c r="G265" s="43"/>
       <c r="H265" s="44"/>
     </row>
-    <row r="266" spans="1:28" ht="23.25">
+    <row r="266" spans="1:28" ht="22.8">
       <c r="A266" s="43" t="s">
         <v>587</v>
       </c>
@@ -9852,7 +9856,7 @@
       <c r="G266" s="43"/>
       <c r="H266" s="44"/>
     </row>
-    <row r="267" spans="1:28" ht="23.25">
+    <row r="267" spans="1:28" ht="22.8">
       <c r="A267" s="9"/>
       <c r="B267" s="10" t="s">
         <v>6</v>
@@ -9872,7 +9876,7 @@
       <c r="G267" s="10"/>
       <c r="H267" s="10"/>
     </row>
-    <row r="268" spans="1:28" ht="23.25">
+    <row r="268" spans="1:28" ht="22.8">
       <c r="A268" s="10"/>
       <c r="B268" s="10" t="s">
         <v>250</v>
@@ -9892,7 +9896,7 @@
       <c r="G268" s="10"/>
       <c r="H268" s="10"/>
     </row>
-    <row r="269" spans="1:28" ht="23.25">
+    <row r="269" spans="1:28" ht="22.8">
       <c r="A269" s="10"/>
       <c r="B269" s="10" t="s">
         <v>253</v>
@@ -9912,7 +9916,7 @@
       <c r="G269" s="10"/>
       <c r="H269" s="10"/>
     </row>
-    <row r="270" spans="1:28" ht="23.25">
+    <row r="270" spans="1:28" ht="22.8">
       <c r="A270" s="10"/>
       <c r="B270" s="10" t="s">
         <v>255</v>
@@ -9932,7 +9936,7 @@
       <c r="G270" s="10"/>
       <c r="H270" s="10"/>
     </row>
-    <row r="271" spans="1:28" ht="23.25">
+    <row r="271" spans="1:28" ht="22.8">
       <c r="A271" s="10"/>
       <c r="B271" s="10" t="s">
         <v>258</v>
@@ -9952,7 +9956,7 @@
       <c r="G271" s="10"/>
       <c r="H271" s="10"/>
     </row>
-    <row r="272" spans="1:28" ht="23.25">
+    <row r="272" spans="1:28" ht="22.8">
       <c r="A272" s="10"/>
       <c r="B272" s="10" t="s">
         <v>261</v>
@@ -9972,7 +9976,7 @@
       <c r="G272" s="10"/>
       <c r="H272" s="10"/>
     </row>
-    <row r="273" spans="1:28" ht="23.25">
+    <row r="273" spans="1:28" ht="22.8">
       <c r="A273" s="10"/>
       <c r="B273" s="10" t="s">
         <v>263</v>
@@ -9992,7 +9996,7 @@
       <c r="G273" s="10"/>
       <c r="H273" s="10"/>
     </row>
-    <row r="274" spans="1:28" ht="23.25">
+    <row r="274" spans="1:28" ht="22.8">
       <c r="A274" s="10"/>
       <c r="B274" s="10" t="s">
         <v>265</v>
@@ -10012,7 +10016,7 @@
       <c r="G274" s="10"/>
       <c r="H274" s="10"/>
     </row>
-    <row r="275" spans="1:28" ht="23.25">
+    <row r="275" spans="1:28" ht="22.8">
       <c r="A275" s="10"/>
       <c r="B275" s="10" t="s">
         <v>267</v>
@@ -10032,7 +10036,7 @@
       <c r="G275" s="10"/>
       <c r="H275" s="10"/>
     </row>
-    <row r="276" spans="1:28" ht="23.25">
+    <row r="276" spans="1:28" ht="22.8">
       <c r="A276" s="10"/>
       <c r="B276" s="10" t="s">
         <v>269</v>
@@ -10052,7 +10056,7 @@
       <c r="G276" s="10"/>
       <c r="H276" s="10"/>
     </row>
-    <row r="277" spans="1:28" ht="23.25">
+    <row r="277" spans="1:28" ht="22.8">
       <c r="A277" s="10"/>
       <c r="B277" s="10" t="s">
         <v>271</v>
@@ -10072,7 +10076,7 @@
       <c r="G277" s="10"/>
       <c r="H277" s="10"/>
     </row>
-    <row r="278" spans="1:28" ht="23.25">
+    <row r="278" spans="1:28" ht="22.8">
       <c r="A278" s="10"/>
       <c r="B278" s="10" t="s">
         <v>273</v>
@@ -10092,7 +10096,7 @@
       <c r="G278" s="10"/>
       <c r="H278" s="10"/>
     </row>
-    <row r="279" spans="1:28" ht="23.25">
+    <row r="279" spans="1:28" ht="22.8">
       <c r="A279" s="10"/>
       <c r="B279" s="10" t="s">
         <v>275</v>
@@ -10112,7 +10116,7 @@
       <c r="G279" s="10"/>
       <c r="H279" s="10"/>
     </row>
-    <row r="280" spans="1:28" ht="23.25">
+    <row r="280" spans="1:28" ht="22.8">
       <c r="A280" s="10"/>
       <c r="B280" s="10" t="s">
         <v>277</v>
@@ -10132,7 +10136,7 @@
       <c r="G280" s="10"/>
       <c r="H280" s="10"/>
     </row>
-    <row r="281" spans="1:28" s="74" customFormat="1" ht="23.25">
+    <row r="281" spans="1:28" s="74" customFormat="1" ht="22.8">
       <c r="A281" s="12"/>
       <c r="B281" s="10" t="s">
         <v>279</v>
@@ -10172,7 +10176,7 @@
       <c r="AA281" s="1"/>
       <c r="AB281" s="1"/>
     </row>
-    <row r="282" spans="1:28" s="77" customFormat="1" ht="23.25">
+    <row r="282" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A282" s="75" t="s">
         <v>588</v>
       </c>
@@ -10210,7 +10214,7 @@
       <c r="AA282" s="4"/>
       <c r="AB282" s="4"/>
     </row>
-    <row r="283" spans="1:28" ht="23.25">
+    <row r="283" spans="1:28" ht="22.8">
       <c r="A283" s="10"/>
       <c r="B283" s="10" t="s">
         <v>6</v>
@@ -10232,7 +10236,7 @@
       </c>
       <c r="H283" s="10"/>
     </row>
-    <row r="284" spans="1:28" ht="23.25">
+    <row r="284" spans="1:28" ht="22.8">
       <c r="A284" s="10"/>
       <c r="B284" s="10" t="s">
         <v>12</v>
@@ -10254,7 +10258,7 @@
       </c>
       <c r="H284" s="10"/>
     </row>
-    <row r="285" spans="1:28" ht="23.25">
+    <row r="285" spans="1:28" ht="22.8">
       <c r="A285" s="10"/>
       <c r="B285" s="10" t="s">
         <v>283</v>
@@ -10276,7 +10280,7 @@
       </c>
       <c r="H285" s="10"/>
     </row>
-    <row r="286" spans="1:28" ht="23.25">
+    <row r="286" spans="1:28" ht="22.8">
       <c r="A286" s="10"/>
       <c r="B286" s="10" t="s">
         <v>284</v>
@@ -10298,7 +10302,7 @@
       </c>
       <c r="H286" s="10"/>
     </row>
-    <row r="287" spans="1:28" s="77" customFormat="1" ht="23.25">
+    <row r="287" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A287" s="43" t="s">
         <v>586</v>
       </c>
@@ -10334,7 +10338,7 @@
       <c r="AA287" s="4"/>
       <c r="AB287" s="4"/>
     </row>
-    <row r="288" spans="1:28" ht="23.25">
+    <row r="288" spans="1:28" ht="22.8">
       <c r="A288" s="9"/>
       <c r="B288" s="10" t="s">
         <v>6</v>
@@ -10354,7 +10358,7 @@
       <c r="G288" s="10"/>
       <c r="H288" s="10"/>
     </row>
-    <row r="289" spans="1:28" ht="23.25">
+    <row r="289" spans="1:28" ht="22.8">
       <c r="A289" s="10"/>
       <c r="B289" s="10" t="s">
         <v>250</v>
@@ -10374,7 +10378,7 @@
       <c r="G289" s="10"/>
       <c r="H289" s="10"/>
     </row>
-    <row r="290" spans="1:28" ht="23.25">
+    <row r="290" spans="1:28" ht="22.8">
       <c r="A290" s="10"/>
       <c r="B290" s="10" t="s">
         <v>253</v>
@@ -10394,7 +10398,7 @@
       <c r="G290" s="10"/>
       <c r="H290" s="10"/>
     </row>
-    <row r="291" spans="1:28" ht="23.25">
+    <row r="291" spans="1:28" ht="22.8">
       <c r="A291" s="10"/>
       <c r="B291" s="10" t="s">
         <v>255</v>
@@ -10414,7 +10418,7 @@
       <c r="G291" s="10"/>
       <c r="H291" s="10"/>
     </row>
-    <row r="292" spans="1:28" ht="23.25">
+    <row r="292" spans="1:28" ht="22.8">
       <c r="A292" s="10"/>
       <c r="B292" s="10" t="s">
         <v>258</v>
@@ -10434,7 +10438,7 @@
       <c r="G292" s="10"/>
       <c r="H292" s="10"/>
     </row>
-    <row r="293" spans="1:28" ht="23.25">
+    <row r="293" spans="1:28" ht="22.8">
       <c r="A293" s="10"/>
       <c r="B293" s="10" t="s">
         <v>261</v>
@@ -10454,7 +10458,7 @@
       <c r="G293" s="10"/>
       <c r="H293" s="10"/>
     </row>
-    <row r="294" spans="1:28" ht="23.25">
+    <row r="294" spans="1:28" ht="22.8">
       <c r="A294" s="10"/>
       <c r="B294" s="10" t="s">
         <v>263</v>
@@ -10474,7 +10478,7 @@
       <c r="G294" s="10"/>
       <c r="H294" s="10"/>
     </row>
-    <row r="295" spans="1:28" ht="23.25">
+    <row r="295" spans="1:28" ht="22.8">
       <c r="A295" s="10"/>
       <c r="B295" s="10" t="s">
         <v>265</v>
@@ -10494,7 +10498,7 @@
       <c r="G295" s="10"/>
       <c r="H295" s="10"/>
     </row>
-    <row r="296" spans="1:28" ht="23.25">
+    <row r="296" spans="1:28" ht="22.8">
       <c r="A296" s="10"/>
       <c r="B296" s="10" t="s">
         <v>267</v>
@@ -10514,7 +10518,7 @@
       <c r="G296" s="10"/>
       <c r="H296" s="10"/>
     </row>
-    <row r="297" spans="1:28" ht="23.25">
+    <row r="297" spans="1:28" ht="22.8">
       <c r="A297" s="10"/>
       <c r="B297" s="10" t="s">
         <v>269</v>
@@ -10534,7 +10538,7 @@
       <c r="G297" s="10"/>
       <c r="H297" s="10"/>
     </row>
-    <row r="298" spans="1:28" ht="23.25">
+    <row r="298" spans="1:28" ht="22.8">
       <c r="A298" s="10"/>
       <c r="B298" s="10" t="s">
         <v>271</v>
@@ -10554,7 +10558,7 @@
       <c r="G298" s="10"/>
       <c r="H298" s="10"/>
     </row>
-    <row r="299" spans="1:28" ht="23.25">
+    <row r="299" spans="1:28" ht="22.8">
       <c r="A299" s="10"/>
       <c r="B299" s="10" t="s">
         <v>273</v>
@@ -10574,7 +10578,7 @@
       <c r="G299" s="10"/>
       <c r="H299" s="10"/>
     </row>
-    <row r="300" spans="1:28" ht="23.25">
+    <row r="300" spans="1:28" ht="22.8">
       <c r="A300" s="10"/>
       <c r="B300" s="10" t="s">
         <v>275</v>
@@ -10594,7 +10598,7 @@
       <c r="G300" s="10"/>
       <c r="H300" s="10"/>
     </row>
-    <row r="301" spans="1:28" ht="23.25">
+    <row r="301" spans="1:28" ht="22.8">
       <c r="A301" s="10"/>
       <c r="B301" s="10" t="s">
         <v>277</v>
@@ -10614,7 +10618,7 @@
       <c r="G301" s="10"/>
       <c r="H301" s="10"/>
     </row>
-    <row r="302" spans="1:28" s="74" customFormat="1" ht="23.25">
+    <row r="302" spans="1:28" s="74" customFormat="1" ht="22.8">
       <c r="A302" s="12"/>
       <c r="B302" s="10" t="s">
         <v>279</v>
@@ -10654,7 +10658,7 @@
       <c r="AA302" s="1"/>
       <c r="AB302" s="1"/>
     </row>
-    <row r="303" spans="1:28" s="77" customFormat="1" ht="23.25">
+    <row r="303" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A303" s="55" t="s">
         <v>282</v>
       </c>
@@ -10692,7 +10696,7 @@
       <c r="AA303" s="4"/>
       <c r="AB303" s="4"/>
     </row>
-    <row r="304" spans="1:28" ht="23.25">
+    <row r="304" spans="1:28" ht="22.8">
       <c r="A304" s="10"/>
       <c r="B304" s="10" t="s">
         <v>12</v>
@@ -10714,7 +10718,7 @@
       </c>
       <c r="H304" s="10"/>
     </row>
-    <row r="305" spans="1:28" ht="23.25">
+    <row r="305" spans="1:28" ht="22.8">
       <c r="A305" s="10"/>
       <c r="B305" s="10" t="s">
         <v>6</v>
@@ -10732,7 +10736,7 @@
       <c r="G305" s="10"/>
       <c r="H305" s="10"/>
     </row>
-    <row r="306" spans="1:28" ht="23.25">
+    <row r="306" spans="1:28" ht="22.8">
       <c r="A306" s="10"/>
       <c r="B306" s="10" t="s">
         <v>283</v>
@@ -10754,7 +10758,7 @@
       </c>
       <c r="H306" s="10"/>
     </row>
-    <row r="307" spans="1:28" ht="23.25">
+    <row r="307" spans="1:28" ht="22.8">
       <c r="A307" s="10"/>
       <c r="B307" s="10" t="s">
         <v>284</v>
@@ -10776,7 +10780,7 @@
       </c>
       <c r="H307" s="10"/>
     </row>
-    <row r="308" spans="1:28" ht="23.25">
+    <row r="308" spans="1:28" ht="22.8">
       <c r="A308" s="24"/>
       <c r="B308" s="54"/>
       <c r="C308" s="54"/>
@@ -10786,19 +10790,19 @@
       <c r="G308" s="54"/>
       <c r="H308" s="54"/>
     </row>
-    <row r="309" spans="1:28" ht="36.75">
-      <c r="A309" s="101" t="s">
+    <row r="309" spans="1:28" ht="37.799999999999997">
+      <c r="A309" s="99" t="s">
         <v>616</v>
       </c>
-      <c r="B309" s="102"/>
-      <c r="C309" s="102"/>
-      <c r="D309" s="102"/>
-      <c r="E309" s="102"/>
-      <c r="F309" s="102"/>
-      <c r="G309" s="102"/>
-      <c r="H309" s="103"/>
-    </row>
-    <row r="310" spans="1:28" s="77" customFormat="1" ht="23.25">
+      <c r="B309" s="100"/>
+      <c r="C309" s="100"/>
+      <c r="D309" s="100"/>
+      <c r="E309" s="100"/>
+      <c r="F309" s="100"/>
+      <c r="G309" s="100"/>
+      <c r="H309" s="101"/>
+    </row>
+    <row r="310" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A310" s="47" t="s">
         <v>288</v>
       </c>
@@ -10836,7 +10840,7 @@
       <c r="AA310" s="4"/>
       <c r="AB310" s="4"/>
     </row>
-    <row r="311" spans="1:28" ht="23.25">
+    <row r="311" spans="1:28" ht="22.8">
       <c r="A311" s="9"/>
       <c r="B311" s="10" t="s">
         <v>66</v>
@@ -10856,7 +10860,7 @@
       <c r="G311" s="10"/>
       <c r="H311" s="10"/>
     </row>
-    <row r="312" spans="1:28" ht="23.25">
+    <row r="312" spans="1:28" ht="22.8">
       <c r="A312" s="71"/>
       <c r="B312" s="10" t="s">
         <v>88</v>
@@ -10876,7 +10880,7 @@
       <c r="G312" s="10"/>
       <c r="H312" s="10"/>
     </row>
-    <row r="313" spans="1:28" ht="23.25">
+    <row r="313" spans="1:28" ht="22.8">
       <c r="A313" s="9"/>
       <c r="B313" s="10" t="s">
         <v>90</v>
@@ -10898,7 +10902,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="314" spans="1:28" ht="23.25">
+    <row r="314" spans="1:28" ht="22.8">
       <c r="A314" s="10"/>
       <c r="B314" s="10" t="s">
         <v>6</v>
@@ -10918,7 +10922,7 @@
       <c r="G314" s="10"/>
       <c r="H314" s="10"/>
     </row>
-    <row r="315" spans="1:28" ht="23.25">
+    <row r="315" spans="1:28" ht="22.8">
       <c r="A315" s="10"/>
       <c r="B315" s="10" t="s">
         <v>292</v>
@@ -10938,7 +10942,7 @@
       <c r="G315" s="10"/>
       <c r="H315" s="10"/>
     </row>
-    <row r="316" spans="1:28" ht="23.25">
+    <row r="316" spans="1:28" ht="22.8">
       <c r="A316" s="10"/>
       <c r="B316" s="10" t="s">
         <v>295</v>
@@ -10958,7 +10962,7 @@
       <c r="G316" s="10"/>
       <c r="H316" s="10"/>
     </row>
-    <row r="317" spans="1:28" ht="23.25">
+    <row r="317" spans="1:28" ht="22.8">
       <c r="A317" s="10"/>
       <c r="B317" s="10" t="s">
         <v>298</v>
@@ -10978,7 +10982,7 @@
       <c r="G317" s="10"/>
       <c r="H317" s="10"/>
     </row>
-    <row r="318" spans="1:28" ht="23.25">
+    <row r="318" spans="1:28" ht="22.8">
       <c r="A318" s="10"/>
       <c r="B318" s="10" t="s">
         <v>301</v>
@@ -10998,7 +11002,7 @@
       <c r="G318" s="10"/>
       <c r="H318" s="10"/>
     </row>
-    <row r="319" spans="1:28" ht="23.25">
+    <row r="319" spans="1:28" ht="22.8">
       <c r="A319" s="10"/>
       <c r="B319" s="10" t="s">
         <v>38</v>
@@ -11018,7 +11022,7 @@
       <c r="G319" s="10"/>
       <c r="H319" s="10"/>
     </row>
-    <row r="320" spans="1:28" ht="23.25">
+    <row r="320" spans="1:28" ht="22.8">
       <c r="A320" s="10"/>
       <c r="B320" s="10" t="s">
         <v>40</v>
@@ -11038,7 +11042,7 @@
       <c r="G320" s="10"/>
       <c r="H320" s="10"/>
     </row>
-    <row r="321" spans="1:28" s="77" customFormat="1" ht="23.25">
+    <row r="321" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A321" s="9" t="s">
         <v>306</v>
       </c>
@@ -11074,7 +11078,7 @@
       <c r="AA321" s="4"/>
       <c r="AB321" s="4"/>
     </row>
-    <row r="322" spans="1:28" ht="23.25">
+    <row r="322" spans="1:28" ht="22.8">
       <c r="A322" s="9"/>
       <c r="B322" s="10" t="s">
         <v>307</v>
@@ -11094,7 +11098,7 @@
       <c r="G322" s="10"/>
       <c r="H322" s="10"/>
     </row>
-    <row r="323" spans="1:28" ht="23.25">
+    <row r="323" spans="1:28" ht="22.8">
       <c r="A323" s="10"/>
       <c r="B323" s="10" t="s">
         <v>308</v>
@@ -11116,7 +11120,7 @@
       </c>
       <c r="H323" s="10"/>
     </row>
-    <row r="324" spans="1:28" ht="23.25">
+    <row r="324" spans="1:28" ht="22.8">
       <c r="A324" s="10"/>
       <c r="B324" s="10" t="s">
         <v>311</v>
@@ -11138,7 +11142,7 @@
       </c>
       <c r="H324" s="10"/>
     </row>
-    <row r="325" spans="1:28" ht="23.25">
+    <row r="325" spans="1:28" ht="22.8">
       <c r="A325" s="10"/>
       <c r="B325" s="10" t="s">
         <v>314</v>
@@ -11160,7 +11164,7 @@
       </c>
       <c r="H325" s="10"/>
     </row>
-    <row r="326" spans="1:28" ht="23.25">
+    <row r="326" spans="1:28" ht="22.8">
       <c r="A326" s="10"/>
       <c r="B326" s="10" t="s">
         <v>244</v>
@@ -11180,7 +11184,7 @@
       <c r="G326" s="10"/>
       <c r="H326" s="10"/>
     </row>
-    <row r="327" spans="1:28" ht="23.25">
+    <row r="327" spans="1:28" ht="22.8">
       <c r="A327" s="10"/>
       <c r="B327" s="10" t="s">
         <v>319</v>
@@ -11200,7 +11204,7 @@
       <c r="G327" s="10"/>
       <c r="H327" s="10"/>
     </row>
-    <row r="328" spans="1:28" ht="23.25">
+    <row r="328" spans="1:28" ht="22.8">
       <c r="A328" s="10"/>
       <c r="B328" s="10" t="s">
         <v>322</v>
@@ -11220,7 +11224,7 @@
       <c r="G328" s="10"/>
       <c r="H328" s="10"/>
     </row>
-    <row r="329" spans="1:28" ht="23.25">
+    <row r="329" spans="1:28" ht="22.8">
       <c r="A329" s="10"/>
       <c r="B329" s="10" t="s">
         <v>325</v>
@@ -11240,7 +11244,7 @@
       <c r="G329" s="10"/>
       <c r="H329" s="10"/>
     </row>
-    <row r="330" spans="1:28" ht="23.25">
+    <row r="330" spans="1:28" ht="22.8">
       <c r="A330" s="10"/>
       <c r="B330" s="10" t="s">
         <v>328</v>
@@ -11260,7 +11264,7 @@
       <c r="G330" s="10"/>
       <c r="H330" s="10"/>
     </row>
-    <row r="331" spans="1:28" ht="23.25">
+    <row r="331" spans="1:28" ht="22.8">
       <c r="A331" s="10"/>
       <c r="B331" s="10" t="s">
         <v>331</v>
@@ -11280,7 +11284,7 @@
       <c r="G331" s="10"/>
       <c r="H331" s="10"/>
     </row>
-    <row r="332" spans="1:28" s="77" customFormat="1" ht="23.25">
+    <row r="332" spans="1:28" s="77" customFormat="1" ht="22.8">
       <c r="A332" s="9" t="s">
         <v>334</v>
       </c>
@@ -11316,7 +11320,7 @@
       <c r="AA332" s="4"/>
       <c r="AB332" s="4"/>
     </row>
-    <row r="333" spans="1:28" ht="23.25">
+    <row r="333" spans="1:28" ht="22.8">
       <c r="A333" s="9"/>
       <c r="B333" s="10" t="s">
         <v>307</v>
@@ -11336,7 +11340,7 @@
       <c r="G333" s="10"/>
       <c r="H333" s="10"/>
     </row>
-    <row r="334" spans="1:28" ht="23.25">
+    <row r="334" spans="1:28" ht="22.8">
       <c r="A334" s="10"/>
       <c r="B334" s="10" t="s">
         <v>336</v>
@@ -11358,7 +11362,7 @@
       </c>
       <c r="H334" s="10"/>
     </row>
-    <row r="335" spans="1:28" ht="23.25">
+    <row r="335" spans="1:28" ht="22.8">
       <c r="A335" s="10"/>
       <c r="B335" s="10" t="s">
         <v>210</v>
@@ -11380,7 +11384,7 @@
       </c>
       <c r="H335" s="10"/>
     </row>
-    <row r="336" spans="1:28" ht="23.25">
+    <row r="336" spans="1:28" ht="22.8">
       <c r="A336" s="10"/>
       <c r="B336" s="10" t="s">
         <v>244</v>
@@ -11400,7 +11404,7 @@
       <c r="G336" s="10"/>
       <c r="H336" s="10"/>
     </row>
-    <row r="337" spans="1:8" ht="23.25">
+    <row r="337" spans="1:8" ht="22.8">
       <c r="A337" s="10"/>
       <c r="B337" s="10" t="s">
         <v>319</v>
@@ -11420,7 +11424,7 @@
       <c r="G337" s="10"/>
       <c r="H337" s="10"/>
     </row>
-    <row r="338" spans="1:8" ht="23.25">
+    <row r="338" spans="1:8" ht="22.8">
       <c r="A338" s="10"/>
       <c r="B338" s="10" t="s">
         <v>322</v>
@@ -11440,7 +11444,7 @@
       <c r="G338" s="10"/>
       <c r="H338" s="10"/>
     </row>
-    <row r="339" spans="1:8" ht="23.25">
+    <row r="339" spans="1:8" ht="22.8">
       <c r="A339" s="10"/>
       <c r="B339" s="10" t="s">
         <v>325</v>
@@ -11460,7 +11464,7 @@
       <c r="G339" s="10"/>
       <c r="H339" s="10"/>
     </row>
-    <row r="340" spans="1:8" ht="23.25">
+    <row r="340" spans="1:8" ht="22.8">
       <c r="A340" s="10"/>
       <c r="B340" s="10" t="s">
         <v>328</v>
@@ -11480,7 +11484,7 @@
       <c r="G340" s="10"/>
       <c r="H340" s="10"/>
     </row>
-    <row r="341" spans="1:8" ht="23.25">
+    <row r="341" spans="1:8" ht="22.8">
       <c r="A341" s="10"/>
       <c r="B341" s="10" t="s">
         <v>331</v>
@@ -11510,7 +11514,7 @@
       <c r="G342" s="53"/>
       <c r="H342" s="53"/>
     </row>
-    <row r="343" spans="1:8" ht="23.25">
+    <row r="343" spans="1:8" ht="22.8">
       <c r="A343" s="54"/>
       <c r="B343" s="54"/>
       <c r="C343" s="54"/>
@@ -18697,19 +18701,19 @@
   <dimension ref="A1:O69"/>
   <sheetFormatPr defaultRowHeight="21" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" style="15" customWidth="1"/>
-    <col min="2" max="2" width="29.42578125" customWidth="1"/>
-    <col min="3" max="3" width="52.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" style="15" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" customWidth="1"/>
+    <col min="3" max="3" width="52.6640625" customWidth="1"/>
     <col min="4" max="4" width="55" style="14" customWidth="1"/>
-    <col min="5" max="5" width="27.28515625" style="19" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="53.85546875" style="14" customWidth="1"/>
-    <col min="7" max="7" width="66.140625" style="14" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="14" customWidth="1"/>
-    <col min="9" max="9" width="29.42578125" style="14" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.42578125" customWidth="1"/>
-    <col min="18" max="18" width="24.7109375" customWidth="1"/>
+    <col min="5" max="5" width="27.33203125" style="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="53.88671875" style="14" customWidth="1"/>
+    <col min="7" max="7" width="66.109375" style="14" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" style="14" customWidth="1"/>
+    <col min="9" max="9" width="29.44140625" style="14" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" customWidth="1"/>
+    <col min="16" max="16" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.44140625" customWidth="1"/>
+    <col min="18" max="18" width="24.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" customHeight="1">
@@ -18742,11 +18746,11 @@
       </c>
       <c r="J1" s="7"/>
     </row>
-    <row r="2" spans="1:15" ht="26.45" customHeight="1">
-      <c r="A2" s="97" t="s">
+    <row r="2" spans="1:15" ht="26.4" customHeight="1">
+      <c r="A2" s="98" t="s">
         <v>441</v>
       </c>
-      <c r="B2" s="98" t="s">
+      <c r="B2" s="97" t="s">
         <v>761</v>
       </c>
       <c r="C2" s="96" t="s">
@@ -18772,8 +18776,8 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="24" customHeight="1">
-      <c r="A3" s="97"/>
-      <c r="B3" s="98"/>
+      <c r="A3" s="98"/>
+      <c r="B3" s="97"/>
       <c r="C3" s="96"/>
       <c r="D3" s="81" t="s">
         <v>446</v>
@@ -18796,7 +18800,7 @@
       <c r="J3" s="7"/>
     </row>
     <row r="4" spans="1:15" ht="21" customHeight="1">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="98" t="s">
         <v>529</v>
       </c>
       <c r="B4" s="96" t="s">
@@ -18824,7 +18828,7 @@
       <c r="J4" s="7"/>
     </row>
     <row r="5" spans="1:15" ht="21" customHeight="1">
-      <c r="A5" s="97"/>
+      <c r="A5" s="98"/>
       <c r="B5" s="96"/>
       <c r="C5" s="96"/>
       <c r="D5" s="81" t="s">
@@ -18846,7 +18850,7 @@
       <c r="J5" s="7"/>
     </row>
     <row r="6" spans="1:15" ht="21" customHeight="1">
-      <c r="A6" s="97"/>
+      <c r="A6" s="98"/>
       <c r="B6" s="96"/>
       <c r="C6" s="96"/>
       <c r="D6" s="81" t="s">
@@ -18868,7 +18872,7 @@
       <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:15" ht="21" customHeight="1">
-      <c r="A7" s="97"/>
+      <c r="A7" s="98"/>
       <c r="B7" s="96"/>
       <c r="C7" s="96"/>
       <c r="D7" s="81" t="s">
@@ -18888,10 +18892,10 @@
       </c>
       <c r="I7" s="83"/>
       <c r="J7" s="7"/>
-      <c r="O7" s="99"/>
+      <c r="O7" s="94"/>
     </row>
     <row r="8" spans="1:15" ht="21" customHeight="1">
-      <c r="A8" s="97"/>
+      <c r="A8" s="98"/>
       <c r="B8" s="96"/>
       <c r="C8" s="96"/>
       <c r="D8" s="81" t="s">
@@ -18911,10 +18915,10 @@
       </c>
       <c r="I8" s="83"/>
       <c r="J8" s="7"/>
-      <c r="O8" s="100"/>
+      <c r="O8" s="95"/>
     </row>
     <row r="9" spans="1:15" ht="21" customHeight="1">
-      <c r="A9" s="97" t="s">
+      <c r="A9" s="98" t="s">
         <v>540</v>
       </c>
       <c r="B9" s="96" t="s">
@@ -18942,7 +18946,7 @@
       <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:15" ht="21" customHeight="1">
-      <c r="A10" s="97"/>
+      <c r="A10" s="98"/>
       <c r="B10" s="96"/>
       <c r="C10" s="96"/>
       <c r="D10" s="81" t="s">
@@ -18964,7 +18968,7 @@
       <c r="J10" s="7"/>
     </row>
     <row r="11" spans="1:15" ht="21" customHeight="1">
-      <c r="A11" s="97"/>
+      <c r="A11" s="98"/>
       <c r="B11" s="96"/>
       <c r="C11" s="96"/>
       <c r="D11" s="81" t="s">
@@ -18985,8 +18989,8 @@
       <c r="I11" s="89"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="1:15" ht="23.45" customHeight="1">
-      <c r="A12" s="97"/>
+    <row r="12" spans="1:15" ht="23.4" customHeight="1">
+      <c r="A12" s="98"/>
       <c r="B12" s="96"/>
       <c r="C12" s="96"/>
       <c r="D12" s="81" t="s">
@@ -19009,8 +19013,8 @@
       </c>
       <c r="J12" s="7"/>
     </row>
-    <row r="13" spans="1:15" ht="23.45" customHeight="1">
-      <c r="A13" s="97"/>
+    <row r="13" spans="1:15" ht="23.4" customHeight="1">
+      <c r="A13" s="98"/>
       <c r="B13" s="96"/>
       <c r="C13" s="96"/>
       <c r="D13" s="81" t="s">
@@ -19034,7 +19038,7 @@
       <c r="J13" s="7"/>
     </row>
     <row r="14" spans="1:15" ht="27" customHeight="1">
-      <c r="A14" s="97"/>
+      <c r="A14" s="98"/>
       <c r="B14" s="96"/>
       <c r="C14" s="96"/>
       <c r="D14" s="81" t="s">
@@ -19057,8 +19061,8 @@
       </c>
       <c r="J14" s="7"/>
     </row>
-    <row r="15" spans="1:15" ht="23.25">
-      <c r="A15" s="97"/>
+    <row r="15" spans="1:15" ht="22.8">
+      <c r="A15" s="98"/>
       <c r="B15" s="96"/>
       <c r="C15" s="96"/>
       <c r="D15" s="81" t="s">
@@ -19081,8 +19085,8 @@
       </c>
       <c r="J15" s="7"/>
     </row>
-    <row r="16" spans="1:15" ht="23.45" customHeight="1">
-      <c r="A16" s="97"/>
+    <row r="16" spans="1:15" ht="23.4" customHeight="1">
+      <c r="A16" s="98"/>
       <c r="B16" s="96"/>
       <c r="C16" s="96"/>
       <c r="D16" s="81" t="s">
@@ -19104,7 +19108,7 @@
       <c r="J16" s="7"/>
     </row>
     <row r="17" spans="1:10" ht="27" customHeight="1">
-      <c r="A17" s="97"/>
+      <c r="A17" s="98"/>
       <c r="B17" s="96"/>
       <c r="C17" s="96"/>
       <c r="D17" s="81" t="s">
@@ -19128,7 +19132,7 @@
       <c r="J17" s="7"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="97" t="s">
+      <c r="A18" s="98" t="s">
         <v>467</v>
       </c>
       <c r="B18" s="96" t="s">
@@ -19156,7 +19160,7 @@
       <c r="J18" s="7"/>
     </row>
     <row r="19" spans="1:10" ht="21" customHeight="1">
-      <c r="A19" s="97"/>
+      <c r="A19" s="98"/>
       <c r="B19" s="96"/>
       <c r="C19" s="96"/>
       <c r="D19" s="81" t="s">
@@ -19178,7 +19182,7 @@
       <c r="J19" s="7"/>
     </row>
     <row r="20" spans="1:10" ht="21" customHeight="1">
-      <c r="A20" s="97"/>
+      <c r="A20" s="98"/>
       <c r="B20" s="96"/>
       <c r="C20" s="96"/>
       <c r="D20" s="81" t="s">
@@ -19200,7 +19204,7 @@
       <c r="J20" s="7"/>
     </row>
     <row r="21" spans="1:10" ht="21" customHeight="1">
-      <c r="A21" s="97"/>
+      <c r="A21" s="98"/>
       <c r="B21" s="96"/>
       <c r="C21" s="96"/>
       <c r="D21" s="81" t="s">
@@ -19222,7 +19226,7 @@
       <c r="J21" s="7"/>
     </row>
     <row r="22" spans="1:10" ht="21" customHeight="1">
-      <c r="A22" s="97"/>
+      <c r="A22" s="98"/>
       <c r="B22" s="96"/>
       <c r="C22" s="96"/>
       <c r="D22" s="81" t="s">
@@ -19244,7 +19248,7 @@
       <c r="J22" s="7"/>
     </row>
     <row r="23" spans="1:10" ht="21" customHeight="1">
-      <c r="A23" s="97"/>
+      <c r="A23" s="98"/>
       <c r="B23" s="96"/>
       <c r="C23" s="96"/>
       <c r="D23" s="81" t="s">
@@ -19266,7 +19270,7 @@
       <c r="J23" s="7"/>
     </row>
     <row r="24" spans="1:10" ht="21" customHeight="1">
-      <c r="A24" s="97"/>
+      <c r="A24" s="98"/>
       <c r="B24" s="96"/>
       <c r="C24" s="96"/>
       <c r="D24" s="81" t="s">
@@ -19288,7 +19292,7 @@
       <c r="J24" s="7"/>
     </row>
     <row r="25" spans="1:10" ht="21" customHeight="1">
-      <c r="A25" s="97"/>
+      <c r="A25" s="98"/>
       <c r="B25" s="96"/>
       <c r="C25" s="96"/>
       <c r="D25" s="81" t="s">
@@ -19310,7 +19314,7 @@
       <c r="J25" s="7"/>
     </row>
     <row r="26" spans="1:10" ht="21" customHeight="1">
-      <c r="A26" s="97"/>
+      <c r="A26" s="98"/>
       <c r="B26" s="96"/>
       <c r="C26" s="96"/>
       <c r="D26" s="81" t="s">
@@ -19334,7 +19338,7 @@
       <c r="J26" s="7"/>
     </row>
     <row r="27" spans="1:10" ht="21" customHeight="1">
-      <c r="A27" s="97"/>
+      <c r="A27" s="98"/>
       <c r="B27" s="96"/>
       <c r="C27" s="96"/>
       <c r="D27" s="81" t="s">
@@ -19358,7 +19362,7 @@
       <c r="J27" s="7"/>
     </row>
     <row r="28" spans="1:10" ht="21" customHeight="1">
-      <c r="A28" s="97"/>
+      <c r="A28" s="98"/>
       <c r="B28" s="96"/>
       <c r="C28" s="96"/>
       <c r="D28" s="81" t="s">
@@ -19380,7 +19384,7 @@
       <c r="J28" s="7"/>
     </row>
     <row r="29" spans="1:10" ht="21" customHeight="1">
-      <c r="A29" s="97"/>
+      <c r="A29" s="98"/>
       <c r="B29" s="96"/>
       <c r="C29" s="96"/>
       <c r="D29" s="81" t="s">
@@ -19404,7 +19408,7 @@
       <c r="J29" s="7"/>
     </row>
     <row r="30" spans="1:10" ht="21" customHeight="1">
-      <c r="A30" s="97"/>
+      <c r="A30" s="98"/>
       <c r="B30" s="96"/>
       <c r="C30" s="96"/>
       <c r="D30" s="81" t="s">
@@ -19426,7 +19430,7 @@
       <c r="J30" s="7"/>
     </row>
     <row r="31" spans="1:10" ht="21" customHeight="1">
-      <c r="A31" s="97"/>
+      <c r="A31" s="98"/>
       <c r="B31" s="96"/>
       <c r="C31" s="96"/>
       <c r="D31" s="81" t="s">
@@ -19450,7 +19454,7 @@
       <c r="J31" s="7"/>
     </row>
     <row r="32" spans="1:10" ht="21" customHeight="1">
-      <c r="A32" s="97"/>
+      <c r="A32" s="98"/>
       <c r="B32" s="96"/>
       <c r="C32" s="96"/>
       <c r="D32" s="81" t="s">
@@ -19472,7 +19476,7 @@
       <c r="J32" s="7"/>
     </row>
     <row r="33" spans="1:10" ht="21" customHeight="1">
-      <c r="A33" s="97"/>
+      <c r="A33" s="98"/>
       <c r="B33" s="96"/>
       <c r="C33" s="96"/>
       <c r="D33" s="81" t="s">
@@ -19494,13 +19498,13 @@
       <c r="J33" s="7"/>
     </row>
     <row r="34" spans="1:10" ht="21" customHeight="1">
-      <c r="A34" s="97" t="s">
+      <c r="A34" s="98" t="s">
         <v>502</v>
       </c>
       <c r="B34" s="96" t="s">
         <v>503</v>
       </c>
-      <c r="C34" s="98" t="s">
+      <c r="C34" s="97" t="s">
         <v>504</v>
       </c>
       <c r="D34" s="81" t="s">
@@ -19522,9 +19526,9 @@
       <c r="J34" s="7"/>
     </row>
     <row r="35" spans="1:10" ht="21" customHeight="1">
-      <c r="A35" s="97"/>
+      <c r="A35" s="98"/>
       <c r="B35" s="96"/>
-      <c r="C35" s="98"/>
+      <c r="C35" s="97"/>
       <c r="D35" s="81" t="s">
         <v>451</v>
       </c>
@@ -19544,9 +19548,9 @@
       <c r="J35" s="7"/>
     </row>
     <row r="36" spans="1:10" ht="21" customHeight="1">
-      <c r="A36" s="97"/>
+      <c r="A36" s="98"/>
       <c r="B36" s="96"/>
-      <c r="C36" s="98"/>
+      <c r="C36" s="97"/>
       <c r="D36" s="81" t="s">
         <v>508</v>
       </c>
@@ -19568,9 +19572,9 @@
       <c r="J36" s="7"/>
     </row>
     <row r="37" spans="1:10" ht="21" customHeight="1">
-      <c r="A37" s="97"/>
+      <c r="A37" s="98"/>
       <c r="B37" s="96"/>
-      <c r="C37" s="98"/>
+      <c r="C37" s="97"/>
       <c r="D37" s="81" t="s">
         <v>510</v>
       </c>
@@ -19592,9 +19596,9 @@
       <c r="J37" s="7"/>
     </row>
     <row r="38" spans="1:10" ht="21" customHeight="1">
-      <c r="A38" s="97"/>
+      <c r="A38" s="98"/>
       <c r="B38" s="96"/>
-      <c r="C38" s="98"/>
+      <c r="C38" s="97"/>
       <c r="D38" s="81" t="s">
         <v>452</v>
       </c>
@@ -19616,9 +19620,9 @@
       <c r="J38" s="7"/>
     </row>
     <row r="39" spans="1:10" ht="21" customHeight="1">
-      <c r="A39" s="97"/>
+      <c r="A39" s="98"/>
       <c r="B39" s="96"/>
-      <c r="C39" s="98"/>
+      <c r="C39" s="97"/>
       <c r="D39" s="81" t="s">
         <v>512</v>
       </c>
@@ -19638,9 +19642,9 @@
       <c r="J39" s="7"/>
     </row>
     <row r="40" spans="1:10" ht="21" customHeight="1">
-      <c r="A40" s="97"/>
+      <c r="A40" s="98"/>
       <c r="B40" s="96"/>
-      <c r="C40" s="98"/>
+      <c r="C40" s="97"/>
       <c r="D40" s="81" t="s">
         <v>514</v>
       </c>
@@ -19660,9 +19664,9 @@
       <c r="J40" s="7"/>
     </row>
     <row r="41" spans="1:10" ht="21" customHeight="1">
-      <c r="A41" s="97"/>
+      <c r="A41" s="98"/>
       <c r="B41" s="96"/>
-      <c r="C41" s="98"/>
+      <c r="C41" s="97"/>
       <c r="D41" s="81" t="s">
         <v>516</v>
       </c>
@@ -19682,9 +19686,9 @@
       <c r="J41" s="7"/>
     </row>
     <row r="42" spans="1:10" ht="21" customHeight="1">
-      <c r="A42" s="97"/>
+      <c r="A42" s="98"/>
       <c r="B42" s="96"/>
-      <c r="C42" s="98"/>
+      <c r="C42" s="97"/>
       <c r="D42" s="81" t="s">
         <v>518</v>
       </c>
@@ -19706,9 +19710,9 @@
       <c r="J42" s="7"/>
     </row>
     <row r="43" spans="1:10" ht="21" customHeight="1">
-      <c r="A43" s="97"/>
+      <c r="A43" s="98"/>
       <c r="B43" s="96"/>
-      <c r="C43" s="98"/>
+      <c r="C43" s="97"/>
       <c r="D43" s="81" t="s">
         <v>461</v>
       </c>
@@ -19730,9 +19734,9 @@
       <c r="J43" s="7"/>
     </row>
     <row r="44" spans="1:10" ht="21" customHeight="1">
-      <c r="A44" s="97"/>
+      <c r="A44" s="98"/>
       <c r="B44" s="96"/>
-      <c r="C44" s="98"/>
+      <c r="C44" s="97"/>
       <c r="D44" s="81" t="s">
         <v>458</v>
       </c>
@@ -19754,9 +19758,9 @@
       <c r="J44" s="7"/>
     </row>
     <row r="45" spans="1:10" ht="21" customHeight="1">
-      <c r="A45" s="97"/>
+      <c r="A45" s="98"/>
       <c r="B45" s="96"/>
-      <c r="C45" s="98"/>
+      <c r="C45" s="97"/>
       <c r="D45" s="81" t="s">
         <v>520</v>
       </c>
@@ -19778,10 +19782,10 @@
       <c r="J45" s="7"/>
     </row>
     <row r="46" spans="1:10" ht="21" customHeight="1">
-      <c r="A46" s="97"/>
+      <c r="A46" s="98"/>
       <c r="B46" s="96"/>
-      <c r="C46" s="98"/>
-      <c r="D46" s="94" t="s">
+      <c r="C46" s="97"/>
+      <c r="D46" s="112" t="s">
         <v>772</v>
       </c>
       <c r="E46" s="82" t="s">
@@ -19802,10 +19806,10 @@
       <c r="J46" s="7"/>
     </row>
     <row r="47" spans="1:10" ht="21" customHeight="1">
-      <c r="A47" s="97"/>
+      <c r="A47" s="98"/>
       <c r="B47" s="96"/>
-      <c r="C47" s="98"/>
-      <c r="D47" s="94" t="s">
+      <c r="C47" s="97"/>
+      <c r="D47" s="112" t="s">
         <v>773</v>
       </c>
       <c r="E47" s="82" t="s">
@@ -19824,7 +19828,7 @@
       <c r="J47" s="7"/>
     </row>
     <row r="48" spans="1:10" ht="21.6" customHeight="1">
-      <c r="A48" s="97" t="s">
+      <c r="A48" s="98" t="s">
         <v>522</v>
       </c>
       <c r="B48" s="96" t="s">
@@ -19833,7 +19837,7 @@
       <c r="C48" s="96" t="s">
         <v>524</v>
       </c>
-      <c r="D48" s="86" t="s">
+      <c r="D48" s="113" t="s">
         <v>505</v>
       </c>
       <c r="E48" s="82" t="s">
@@ -19852,7 +19856,7 @@
       <c r="J48" s="7"/>
     </row>
     <row r="49" spans="1:10" ht="21" customHeight="1">
-      <c r="A49" s="97"/>
+      <c r="A49" s="98"/>
       <c r="B49" s="96"/>
       <c r="C49" s="96"/>
       <c r="D49" s="81" t="s">
@@ -19874,7 +19878,7 @@
       <c r="J49" s="7"/>
     </row>
     <row r="50" spans="1:10" ht="21" customHeight="1">
-      <c r="A50" s="97"/>
+      <c r="A50" s="98"/>
       <c r="B50" s="96"/>
       <c r="C50" s="96"/>
       <c r="D50" s="81" t="s">
@@ -19896,16 +19900,16 @@
       <c r="J50" s="7"/>
     </row>
     <row r="51" spans="1:10" ht="21" customHeight="1">
-      <c r="A51" s="97" t="s">
+      <c r="A51" s="98" t="s">
         <v>783</v>
       </c>
       <c r="B51" s="96" t="s">
         <v>449</v>
       </c>
-      <c r="C51" s="98" t="s">
+      <c r="C51" s="97" t="s">
         <v>760</v>
       </c>
-      <c r="D51" s="94" t="s">
+      <c r="D51" s="112" t="s">
         <v>766</v>
       </c>
       <c r="E51" s="82" t="s">
@@ -19924,9 +19928,9 @@
       <c r="J51" s="7"/>
     </row>
     <row r="52" spans="1:10" ht="21" customHeight="1">
-      <c r="A52" s="97"/>
+      <c r="A52" s="98"/>
       <c r="B52" s="96"/>
-      <c r="C52" s="98"/>
+      <c r="C52" s="97"/>
       <c r="D52" s="81" t="s">
         <v>767</v>
       </c>
@@ -19946,9 +19950,9 @@
       <c r="J52" s="7"/>
     </row>
     <row r="53" spans="1:10" s="85" customFormat="1" ht="24" customHeight="1">
-      <c r="A53" s="97"/>
+      <c r="A53" s="98"/>
       <c r="B53" s="96"/>
-      <c r="C53" s="98"/>
+      <c r="C53" s="97"/>
       <c r="D53" s="81" t="s">
         <v>452</v>
       </c>
@@ -19970,10 +19974,10 @@
       <c r="J53" s="84"/>
     </row>
     <row r="54" spans="1:10" ht="21" customHeight="1">
-      <c r="A54" s="97"/>
+      <c r="A54" s="98"/>
       <c r="B54" s="96"/>
-      <c r="C54" s="98"/>
-      <c r="D54" s="94" t="s">
+      <c r="C54" s="97"/>
+      <c r="D54" s="112" t="s">
         <v>768</v>
       </c>
       <c r="E54" s="82" t="s">
@@ -19994,9 +19998,9 @@
       <c r="J54" s="7"/>
     </row>
     <row r="55" spans="1:10" ht="21" customHeight="1">
-      <c r="A55" s="97"/>
+      <c r="A55" s="98"/>
       <c r="B55" s="96"/>
-      <c r="C55" s="98"/>
+      <c r="C55" s="97"/>
       <c r="D55" s="81" t="s">
         <v>456</v>
       </c>
@@ -20018,9 +20022,9 @@
       <c r="J55" s="7"/>
     </row>
     <row r="56" spans="1:10" ht="21" customHeight="1">
-      <c r="A56" s="97"/>
+      <c r="A56" s="98"/>
       <c r="B56" s="96"/>
-      <c r="C56" s="98"/>
+      <c r="C56" s="97"/>
       <c r="D56" s="81" t="s">
         <v>458</v>
       </c>
@@ -20042,10 +20046,10 @@
       <c r="J56" s="7"/>
     </row>
     <row r="57" spans="1:10" ht="21" customHeight="1">
-      <c r="A57" s="97"/>
+      <c r="A57" s="98"/>
       <c r="B57" s="96"/>
-      <c r="C57" s="98"/>
-      <c r="D57" s="95" t="s">
+      <c r="C57" s="97"/>
+      <c r="D57" s="114" t="s">
         <v>769</v>
       </c>
       <c r="E57" s="82" t="s">
@@ -20066,11 +20070,11 @@
       <c r="J57" s="7"/>
     </row>
     <row r="58" spans="1:10" ht="21" customHeight="1">
-      <c r="A58" s="97"/>
+      <c r="A58" s="98"/>
       <c r="B58" s="96"/>
-      <c r="C58" s="98"/>
-      <c r="D58" s="94" t="s">
-        <v>456</v>
+      <c r="C58" s="97"/>
+      <c r="D58" s="112" t="s">
+        <v>843</v>
       </c>
       <c r="E58" s="82" t="s">
         <v>7</v>
@@ -20090,10 +20094,10 @@
       <c r="J58" s="7"/>
     </row>
     <row r="59" spans="1:10" ht="21" customHeight="1">
-      <c r="A59" s="97"/>
+      <c r="A59" s="98"/>
       <c r="B59" s="96"/>
-      <c r="C59" s="98"/>
-      <c r="D59" s="95" t="s">
+      <c r="C59" s="97"/>
+      <c r="D59" s="114" t="s">
         <v>770</v>
       </c>
       <c r="E59" s="82" t="s">
@@ -20114,10 +20118,10 @@
       <c r="J59" s="7"/>
     </row>
     <row r="60" spans="1:10" ht="21" customHeight="1">
-      <c r="A60" s="97"/>
+      <c r="A60" s="98"/>
       <c r="B60" s="96"/>
-      <c r="C60" s="98"/>
-      <c r="D60" s="94" t="s">
+      <c r="C60" s="97"/>
+      <c r="D60" s="112" t="s">
         <v>771</v>
       </c>
       <c r="E60" s="82" t="s">
@@ -20138,10 +20142,10 @@
       <c r="J60" s="7"/>
     </row>
     <row r="61" spans="1:10" ht="21" customHeight="1">
-      <c r="A61" s="97"/>
+      <c r="A61" s="98"/>
       <c r="B61" s="96"/>
-      <c r="C61" s="98"/>
-      <c r="D61" s="94" t="s">
+      <c r="C61" s="97"/>
+      <c r="D61" s="112" t="s">
         <v>772</v>
       </c>
       <c r="E61" s="82" t="s">
@@ -20162,10 +20166,10 @@
       <c r="J61" s="7"/>
     </row>
     <row r="62" spans="1:10" ht="21" customHeight="1">
-      <c r="A62" s="97"/>
+      <c r="A62" s="98"/>
       <c r="B62" s="96"/>
-      <c r="C62" s="98"/>
-      <c r="D62" s="94" t="s">
+      <c r="C62" s="97"/>
+      <c r="D62" s="112" t="s">
         <v>773</v>
       </c>
       <c r="E62" s="82" t="s">
@@ -20198,11 +20202,15 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="C9:C17"/>
-    <mergeCell ref="C34:C47"/>
-    <mergeCell ref="C48:C50"/>
-    <mergeCell ref="B9:B17"/>
+    <mergeCell ref="C51:C62"/>
+    <mergeCell ref="B51:B62"/>
+    <mergeCell ref="A51:A62"/>
+    <mergeCell ref="A34:A47"/>
+    <mergeCell ref="C18:C33"/>
+    <mergeCell ref="B18:B33"/>
+    <mergeCell ref="A18:A33"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A48:A50"/>
     <mergeCell ref="A9:A17"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
@@ -20210,16 +20218,12 @@
     <mergeCell ref="C4:C8"/>
     <mergeCell ref="B4:B8"/>
     <mergeCell ref="A4:A8"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="C9:C17"/>
+    <mergeCell ref="C34:C47"/>
+    <mergeCell ref="C48:C50"/>
+    <mergeCell ref="B9:B17"/>
     <mergeCell ref="B34:B47"/>
-    <mergeCell ref="A34:A47"/>
-    <mergeCell ref="C18:C33"/>
-    <mergeCell ref="B18:B33"/>
-    <mergeCell ref="A18:A33"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="C51:C62"/>
-    <mergeCell ref="B51:B62"/>
-    <mergeCell ref="A51:A62"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
